--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>6989607</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.31800007820129</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.31800007820129</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>6404308</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.28200006484985</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.3050000667572</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>7941141</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.30599999427795</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.35199999809265</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6425686</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.38199996948242</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.35700011253357</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.35899996757507</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.38199996948242</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>7009859</v>
+        <v>5134335</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.34100008010864</v>
+        <v>2.31500005722046</v>
       </c>
       <c r="D2715" t="n">
-        <v>2.30200004577637</v>
+        <v>2.28699994087219</v>
       </c>
       <c r="E2715" t="n">
         <v>2.3050000667572</v>
       </c>
       <c r="F2715" t="n">
-        <v>2.33800005912781</v>
+        <v>2.31399989128113</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,19 +62819,19 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>11903027</v>
+        <v>7009859</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.35700011253357</v>
+        <v>2.34100008010864</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.30800008773804</v>
+        <v>2.30200004577637</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.33100008964539</v>
+        <v>2.3050000667572</v>
       </c>
       <c r="F2716" t="n">
         <v>2.33800005912781</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>10240094</v>
+        <v>11903027</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.35800004005432</v>
+        <v>2.35700011253357</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.32699990272522</v>
+        <v>2.30800008773804</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.33299994468689</v>
+        <v>2.33100008964539</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.35800004005432</v>
+        <v>2.33800005912781</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>13021715</v>
+        <v>10240094</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.38199996948242</v>
+        <v>2.35800004005432</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.3529999256134</v>
+        <v>2.32699990272522</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.35999989509583</v>
+        <v>2.33299994468689</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.37199997901917</v>
+        <v>2.35800004005432</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>6989607</v>
+        <v>13021715</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.38000011444092</v>
+        <v>2.38199996948242</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.31800007820129</v>
+        <v>2.3529999256134</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.38000011444092</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="F2719" t="n">
-        <v>2.31800007820129</v>
+        <v>2.37199997901917</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>6404308</v>
+        <v>6989607</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.3199999332428</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.28200006484985</v>
+        <v>2.31800007820129</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.3199999332428</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.3050000667572</v>
+        <v>2.31800007820129</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>7941141</v>
+        <v>6404308</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.35999989509583</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.30599999427795</v>
+        <v>2.28200006484985</v>
       </c>
       <c r="E2721" t="n">
-        <v>2.30999994277954</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.35199999809265</v>
+        <v>2.3050000667572</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6425686</v>
+        <v>7941141</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.38199996948242</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="D2722" t="n">
-        <v>2.35700011253357</v>
+        <v>2.30599999427795</v>
       </c>
       <c r="E2722" t="n">
-        <v>2.35899996757507</v>
+        <v>2.30999994277954</v>
       </c>
       <c r="F2722" t="n">
-        <v>2.38199996948242</v>
+        <v>2.35199999809265</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>13407899</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.37599992752075</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.30399990081787</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.31900000572205</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.24399995803833</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.22399997711182</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>6311921</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.28299999237061</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.23699998855591</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.24499988555908</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.24499988555908</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.24900007247925</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>5684115</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.25500011444092</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.24699997901917</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.24699997901917</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.24399995803833</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>6063960</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.28699994087219</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.23300004005432</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.24399995803833</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.24399995803833</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.26999998092651</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>5089763</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.29099988937378</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>11912025</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/A2A.MI.xlsx
+++ b/data/A2A.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.730566501617432</v>
+        <v>0.730566561222076</v>
       </c>
       <c r="H2" t="n">
         <v>12496412</v>
@@ -456,7 +456,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.738922774791718</v>
+        <v>0.738922655582428</v>
       </c>
       <c r="H3" t="n">
         <v>9773848</v>
@@ -485,7 +485,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>0.734147846698761</v>
+        <v>0.734147787094116</v>
       </c>
       <c r="H4" t="n">
         <v>12137840</v>
@@ -572,7 +572,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.740116536617279</v>
+        <v>0.74011641740799</v>
       </c>
       <c r="H7" t="n">
         <v>16012506</v>
@@ -601,7 +601,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G8" t="n">
-        <v>0.702513873577118</v>
+        <v>0.702513813972473</v>
       </c>
       <c r="H8" t="n">
         <v>38278597</v>
@@ -630,7 +630,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G9" t="n">
-        <v>0.694754600524902</v>
+        <v>0.694754540920258</v>
       </c>
       <c r="H9" t="n">
         <v>38161268</v>
@@ -659,7 +659,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G10" t="n">
-        <v>0.676251590251923</v>
+        <v>0.676251530647278</v>
       </c>
       <c r="H10" t="n">
         <v>25217827</v>
@@ -746,7 +746,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G13" t="n">
-        <v>0.654764354228973</v>
+        <v>0.654764413833618</v>
       </c>
       <c r="H13" t="n">
         <v>22502234</v>
@@ -775,7 +775,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>0.632680177688599</v>
+        <v>0.632680118083954</v>
       </c>
       <c r="H14" t="n">
         <v>29796865</v>
@@ -804,7 +804,7 @@
         <v>1.07099997997284</v>
       </c>
       <c r="G15" t="n">
-        <v>0.639245688915253</v>
+        <v>0.639245808124542</v>
       </c>
       <c r="H15" t="n">
         <v>22968792</v>
@@ -920,7 +920,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G19" t="n">
-        <v>0.658345639705658</v>
+        <v>0.658345580101013</v>
       </c>
       <c r="H19" t="n">
         <v>24092591</v>
@@ -1007,7 +1007,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G22" t="n">
-        <v>0.657748758792877</v>
+        <v>0.657748699188232</v>
       </c>
       <c r="H22" t="n">
         <v>10681175</v>
@@ -1036,7 +1036,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G23" t="n">
-        <v>0.645214378833771</v>
+        <v>0.645214438438416</v>
       </c>
       <c r="H23" t="n">
         <v>14552227</v>
@@ -1065,7 +1065,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>0.640439391136169</v>
+        <v>0.640439450740814</v>
       </c>
       <c r="H24" t="n">
         <v>14960682</v>
@@ -1094,7 +1094,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G25" t="n">
-        <v>0.636261403560638</v>
+        <v>0.636261343955994</v>
       </c>
       <c r="H25" t="n">
         <v>13434874</v>
@@ -1152,7 +1152,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G27" t="n">
-        <v>0.584333837032318</v>
+        <v>0.584333896636963</v>
       </c>
       <c r="H27" t="n">
         <v>20217944</v>
@@ -1181,7 +1181,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G28" t="n">
-        <v>0.570605933666229</v>
+        <v>0.570605874061584</v>
       </c>
       <c r="H28" t="n">
         <v>26368896</v>
@@ -1210,7 +1210,7 @@
         <v>0.968500018119812</v>
       </c>
       <c r="G29" t="n">
-        <v>0.578066825866699</v>
+        <v>0.578066766262054</v>
       </c>
       <c r="H29" t="n">
         <v>17947955</v>
@@ -1268,7 +1268,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G31" t="n">
-        <v>0.586124420166016</v>
+        <v>0.58612447977066</v>
       </c>
       <c r="H31" t="n">
         <v>16659629</v>
@@ -1384,7 +1384,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G35" t="n">
-        <v>0.617161691188812</v>
+        <v>0.617161631584167</v>
       </c>
       <c r="H35" t="n">
         <v>24147654</v>
@@ -1413,7 +1413,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G36" t="n">
-        <v>0.607014834880829</v>
+        <v>0.607014894485474</v>
       </c>
       <c r="H36" t="n">
         <v>14899951</v>
@@ -1471,7 +1471,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G38" t="n">
-        <v>0.615967810153961</v>
+        <v>0.615967869758606</v>
       </c>
       <c r="H38" t="n">
         <v>9630246</v>
@@ -1500,7 +1500,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G39" t="n">
-        <v>0.61178982257843</v>
+        <v>0.611789703369141</v>
       </c>
       <c r="H39" t="n">
         <v>10895897</v>
@@ -1529,7 +1529,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>0.618355393409729</v>
+        <v>0.618355333805084</v>
       </c>
       <c r="H40" t="n">
         <v>8385073</v>
@@ -1558,7 +1558,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G41" t="n">
-        <v>0.627308428287506</v>
+        <v>0.627308309078217</v>
       </c>
       <c r="H41" t="n">
         <v>9486715</v>
@@ -1587,7 +1587,7 @@
         <v>1.057000041008</v>
       </c>
       <c r="G42" t="n">
-        <v>0.630889713764191</v>
+        <v>0.630889594554901</v>
       </c>
       <c r="H42" t="n">
         <v>9765845</v>
@@ -1645,7 +1645,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>0.635664522647858</v>
+        <v>0.635664641857147</v>
       </c>
       <c r="H44" t="n">
         <v>12782294</v>
@@ -1732,7 +1732,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G47" t="n">
-        <v>0.628502130508423</v>
+        <v>0.628502070903778</v>
       </c>
       <c r="H47" t="n">
         <v>8526307</v>
@@ -1761,7 +1761,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G48" t="n">
-        <v>0.621936619281769</v>
+        <v>0.621936559677124</v>
       </c>
       <c r="H48" t="n">
         <v>9655546</v>
@@ -1819,7 +1819,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G50" t="n">
-        <v>0.638649046421051</v>
+        <v>0.638648986816406</v>
       </c>
       <c r="H50" t="n">
         <v>16429714</v>
@@ -1848,7 +1848,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G51" t="n">
-        <v>0.680429697036743</v>
+        <v>0.680429637432098</v>
       </c>
       <c r="H51" t="n">
         <v>23278775</v>
@@ -1877,7 +1877,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>0.661329984664917</v>
+        <v>0.661329865455627</v>
       </c>
       <c r="H52" t="n">
         <v>15694552</v>
@@ -1906,7 +1906,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G53" t="n">
-        <v>0.65953928232193</v>
+        <v>0.659539222717285</v>
       </c>
       <c r="H53" t="n">
         <v>6507402</v>
@@ -1993,7 +1993,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G56" t="n">
-        <v>0.664314150810242</v>
+        <v>0.664314270019531</v>
       </c>
       <c r="H56" t="n">
         <v>9301157</v>
@@ -2051,7 +2051,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>0.65953928232193</v>
+        <v>0.659539222717285</v>
       </c>
       <c r="H58" t="n">
         <v>11115013</v>
@@ -2138,7 +2138,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G61" t="n">
-        <v>0.667298555374146</v>
+        <v>0.66729861497879</v>
       </c>
       <c r="H61" t="n">
         <v>6753760</v>
@@ -2196,7 +2196,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>0.682220280170441</v>
+        <v>0.682220220565796</v>
       </c>
       <c r="H63" t="n">
         <v>19874066</v>
@@ -2225,7 +2225,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G64" t="n">
-        <v>0.670282900333405</v>
+        <v>0.670282959938049</v>
       </c>
       <c r="H64" t="n">
         <v>11251150</v>
@@ -2254,7 +2254,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>0.682220280170441</v>
+        <v>0.682220220565796</v>
       </c>
       <c r="H65" t="n">
         <v>20386953</v>
@@ -2283,7 +2283,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G66" t="n">
-        <v>0.673267245292664</v>
+        <v>0.673267304897308</v>
       </c>
       <c r="H66" t="n">
         <v>15485074</v>
@@ -2312,7 +2312,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G67" t="n">
-        <v>0.701916933059692</v>
+        <v>0.701916873455048</v>
       </c>
       <c r="H67" t="n">
         <v>17246846</v>
@@ -2341,7 +2341,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G68" t="n">
-        <v>0.706691920757294</v>
+        <v>0.706691801548004</v>
       </c>
       <c r="H68" t="n">
         <v>24702058</v>
@@ -2457,7 +2457,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>0.716241776943207</v>
+        <v>0.716241657733917</v>
       </c>
       <c r="H72" t="n">
         <v>14486598</v>
@@ -2486,7 +2486,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G73" t="n">
-        <v>0.719822943210602</v>
+        <v>0.719823002815247</v>
       </c>
       <c r="H73" t="n">
         <v>10753177</v>
@@ -2515,7 +2515,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G74" t="n">
-        <v>0.706691920757294</v>
+        <v>0.706691801548004</v>
       </c>
       <c r="H74" t="n">
         <v>8893148</v>
@@ -2544,7 +2544,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G75" t="n">
-        <v>0.716241776943207</v>
+        <v>0.716241657733917</v>
       </c>
       <c r="H75" t="n">
         <v>8885624</v>
@@ -2573,7 +2573,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G76" t="n">
-        <v>0.719822943210602</v>
+        <v>0.719823002815247</v>
       </c>
       <c r="H76" t="n">
         <v>19486416</v>
@@ -2602,7 +2602,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G77" t="n">
-        <v>0.732954144477844</v>
+        <v>0.732954025268555</v>
       </c>
       <c r="H77" t="n">
         <v>12311923</v>
@@ -2631,7 +2631,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G78" t="n">
-        <v>0.722807288169861</v>
+        <v>0.722807347774506</v>
       </c>
       <c r="H78" t="n">
         <v>10052246</v>
@@ -2689,7 +2689,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G80" t="n">
-        <v>0.71803230047226</v>
+        <v>0.718032240867615</v>
       </c>
       <c r="H80" t="n">
         <v>5818495</v>
@@ -2718,7 +2718,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G81" t="n">
-        <v>0.745488226413727</v>
+        <v>0.745488286018372</v>
       </c>
       <c r="H81" t="n">
         <v>15790700</v>
@@ -2747,7 +2747,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G82" t="n">
-        <v>0.742503821849823</v>
+        <v>0.742503881454468</v>
       </c>
       <c r="H82" t="n">
         <v>12292613</v>
@@ -2776,7 +2776,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G83" t="n">
-        <v>0.750263214111328</v>
+        <v>0.750263094902039</v>
       </c>
       <c r="H83" t="n">
         <v>10930530</v>
@@ -2805,7 +2805,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G84" t="n">
-        <v>0.743697643280029</v>
+        <v>0.743697702884674</v>
       </c>
       <c r="H84" t="n">
         <v>7003425</v>
@@ -2834,7 +2834,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G85" t="n">
-        <v>0.733550846576691</v>
+        <v>0.73355096578598</v>
       </c>
       <c r="H85" t="n">
         <v>7033929</v>
@@ -2863,7 +2863,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G86" t="n">
-        <v>0.721016764640808</v>
+        <v>0.721016585826874</v>
       </c>
       <c r="H86" t="n">
         <v>9423788</v>
@@ -2921,7 +2921,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G88" t="n">
-        <v>0.72937285900116</v>
+        <v>0.729372799396515</v>
       </c>
       <c r="H88" t="n">
         <v>6819667</v>
@@ -2950,7 +2950,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>0.735341608524323</v>
+        <v>0.735341489315033</v>
       </c>
       <c r="H89" t="n">
         <v>8426840</v>
@@ -2979,7 +2979,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G90" t="n">
-        <v>0.724597871303558</v>
+        <v>0.724597752094269</v>
       </c>
       <c r="H90" t="n">
         <v>8542557</v>
@@ -3037,7 +3037,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G92" t="n">
-        <v>0.726388394832611</v>
+        <v>0.726388454437256</v>
       </c>
       <c r="H92" t="n">
         <v>9112456</v>
@@ -3066,7 +3066,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>0.734147846698761</v>
+        <v>0.734147787094116</v>
       </c>
       <c r="H93" t="n">
         <v>7627672</v>
@@ -3095,7 +3095,7 @@
         <v>1.22699999809265</v>
       </c>
       <c r="G94" t="n">
-        <v>0.732357263565063</v>
+        <v>0.732357144355774</v>
       </c>
       <c r="H94" t="n">
         <v>6474848</v>
@@ -3124,7 +3124,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>0.734147846698761</v>
+        <v>0.734147787094116</v>
       </c>
       <c r="H95" t="n">
         <v>3717765</v>
@@ -3153,7 +3153,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G96" t="n">
-        <v>0.713257431983948</v>
+        <v>0.713257372379303</v>
       </c>
       <c r="H96" t="n">
         <v>8027078</v>
@@ -3182,7 +3182,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G97" t="n">
-        <v>0.724597871303558</v>
+        <v>0.724597752094269</v>
       </c>
       <c r="H97" t="n">
         <v>5997426</v>
@@ -3211,7 +3211,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G98" t="n">
-        <v>0.717435538768768</v>
+        <v>0.717435479164124</v>
       </c>
       <c r="H98" t="n">
         <v>5147625</v>
@@ -3240,7 +3240,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G99" t="n">
-        <v>0.719822943210602</v>
+        <v>0.719823002815247</v>
       </c>
       <c r="H99" t="n">
         <v>11546937</v>
@@ -3269,7 +3269,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G100" t="n">
-        <v>0.720419883728027</v>
+        <v>0.720419824123383</v>
       </c>
       <c r="H100" t="n">
         <v>8550000</v>
@@ -3356,7 +3356,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G103" t="n">
-        <v>0.745488226413727</v>
+        <v>0.745488286018372</v>
       </c>
       <c r="H103" t="n">
         <v>6218561</v>
@@ -3385,7 +3385,7 @@
         <v>1.25</v>
       </c>
       <c r="G104" t="n">
-        <v>0.746085107326508</v>
+        <v>0.746085047721863</v>
       </c>
       <c r="H104" t="n">
         <v>8207609</v>
@@ -3414,7 +3414,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G105" t="n">
-        <v>0.764587938785553</v>
+        <v>0.764588177204132</v>
       </c>
       <c r="H105" t="n">
         <v>10053871</v>
@@ -3443,7 +3443,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G106" t="n">
-        <v>0.764587938785553</v>
+        <v>0.764588177204132</v>
       </c>
       <c r="H106" t="n">
         <v>17213843</v>
@@ -3472,7 +3472,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G107" t="n">
-        <v>0.768169283866882</v>
+        <v>0.768169224262238</v>
       </c>
       <c r="H107" t="n">
         <v>9484014</v>
@@ -3559,7 +3559,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G110" t="n">
-        <v>0.760410130023956</v>
+        <v>0.760410010814667</v>
       </c>
       <c r="H110" t="n">
         <v>8221702</v>
@@ -3617,7 +3617,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G112" t="n">
-        <v>0.760410130023956</v>
+        <v>0.760410010814667</v>
       </c>
       <c r="H112" t="n">
         <v>7519697</v>
@@ -3646,7 +3646,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G113" t="n">
-        <v>0.765184879302979</v>
+        <v>0.765184938907623</v>
       </c>
       <c r="H113" t="n">
         <v>16794750</v>
@@ -3675,7 +3675,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G114" t="n">
-        <v>0.732954144477844</v>
+        <v>0.732954025268555</v>
       </c>
       <c r="H114" t="n">
         <v>10751587</v>
@@ -3704,7 +3704,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G115" t="n">
-        <v>0.720419883728027</v>
+        <v>0.720419824123383</v>
       </c>
       <c r="H115" t="n">
         <v>9157554</v>
@@ -3733,7 +3733,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G116" t="n">
-        <v>0.702513873577118</v>
+        <v>0.702513813972473</v>
       </c>
       <c r="H116" t="n">
         <v>8888874</v>
@@ -3791,7 +3791,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G118" t="n">
-        <v>0.692367017269135</v>
+        <v>0.69236695766449</v>
       </c>
       <c r="H118" t="n">
         <v>11212688</v>
@@ -3849,7 +3849,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G120" t="n">
-        <v>0.731290638446808</v>
+        <v>0.731290698051453</v>
       </c>
       <c r="H120" t="n">
         <v>11487398</v>
@@ -3907,7 +3907,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G122" t="n">
-        <v>0.716454684734344</v>
+        <v>0.716454744338989</v>
       </c>
       <c r="H122" t="n">
         <v>13603281</v>
@@ -4052,7 +4052,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G127" t="n">
-        <v>0.696673452854156</v>
+        <v>0.696673333644867</v>
       </c>
       <c r="H127" t="n">
         <v>10410928</v>
@@ -4110,7 +4110,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>0.727581799030304</v>
+        <v>0.727581679821014</v>
       </c>
       <c r="H129" t="n">
         <v>7361957</v>
@@ -4139,7 +4139,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G130" t="n">
-        <v>0.734381556510925</v>
+        <v>0.734381496906281</v>
       </c>
       <c r="H130" t="n">
         <v>7031651</v>
@@ -4168,7 +4168,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7232546210289</v>
+        <v>0.723254442214966</v>
       </c>
       <c r="H131" t="n">
         <v>10277364</v>
@@ -4255,7 +4255,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G134" t="n">
-        <v>0.723872661590576</v>
+        <v>0.723872721195221</v>
       </c>
       <c r="H134" t="n">
         <v>10680042</v>
@@ -4284,7 +4284,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G135" t="n">
-        <v>0.727581799030304</v>
+        <v>0.727581679821014</v>
       </c>
       <c r="H135" t="n">
         <v>4896809</v>
@@ -4342,7 +4342,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>0.738708794116974</v>
+        <v>0.738708734512329</v>
       </c>
       <c r="H137" t="n">
         <v>10767784</v>
@@ -4371,7 +4371,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G138" t="n">
-        <v>0.740563094615936</v>
+        <v>0.740563213825226</v>
       </c>
       <c r="H138" t="n">
         <v>9271988</v>
@@ -4487,7 +4487,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G142" t="n">
-        <v>0.754162788391113</v>
+        <v>0.754162847995758</v>
       </c>
       <c r="H142" t="n">
         <v>7243073</v>
@@ -4545,7 +4545,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G144" t="n">
-        <v>0.757871806621552</v>
+        <v>0.757871866226196</v>
       </c>
       <c r="H144" t="n">
         <v>8262835</v>
@@ -4574,7 +4574,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G145" t="n">
-        <v>0.768380641937256</v>
+        <v>0.768380761146545</v>
       </c>
       <c r="H145" t="n">
         <v>7833796</v>
@@ -4632,7 +4632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>0.785071194171906</v>
+        <v>0.78507125377655</v>
       </c>
       <c r="H147" t="n">
         <v>8381593</v>
@@ -4661,7 +4661,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G148" t="n">
-        <v>0.780125677585602</v>
+        <v>0.780125796794891</v>
       </c>
       <c r="H148" t="n">
         <v>5501831</v>
@@ -4690,7 +4690,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>0.785071194171906</v>
+        <v>0.78507125377655</v>
       </c>
       <c r="H149" t="n">
         <v>14448846</v>
@@ -4748,7 +4748,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G151" t="n">
-        <v>0.78445303440094</v>
+        <v>0.78445291519165</v>
       </c>
       <c r="H151" t="n">
         <v>13681600</v>
@@ -4806,7 +4806,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G153" t="n">
-        <v>0.777034997940063</v>
+        <v>0.777035057544708</v>
       </c>
       <c r="H153" t="n">
         <v>5800660</v>
@@ -4835,7 +4835,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G154" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H154" t="n">
         <v>7538498</v>
@@ -4864,7 +4864,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G155" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H155" t="n">
         <v>3167325</v>
@@ -4893,7 +4893,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G156" t="n">
-        <v>0.76776260137558</v>
+        <v>0.76776248216629</v>
       </c>
       <c r="H156" t="n">
         <v>6077048</v>
@@ -4980,7 +4980,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G159" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H159" t="n">
         <v>9127255</v>
@@ -5067,7 +5067,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>0.752308309078217</v>
+        <v>0.752308368682861</v>
       </c>
       <c r="H162" t="n">
         <v>5568229</v>
@@ -5096,7 +5096,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G163" t="n">
-        <v>0.738708794116974</v>
+        <v>0.738708734512329</v>
       </c>
       <c r="H163" t="n">
         <v>8430096</v>
@@ -5125,7 +5125,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G164" t="n">
-        <v>0.736236035823822</v>
+        <v>0.736235976219177</v>
       </c>
       <c r="H164" t="n">
         <v>4967280</v>
@@ -5183,7 +5183,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G166" t="n">
-        <v>0.747363030910492</v>
+        <v>0.747363090515137</v>
       </c>
       <c r="H166" t="n">
         <v>9308218</v>
@@ -5386,7 +5386,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>0.754162788391113</v>
+        <v>0.754162847995758</v>
       </c>
       <c r="H173" t="n">
         <v>9718371</v>
@@ -5415,7 +5415,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G174" t="n">
-        <v>0.749217450618744</v>
+        <v>0.749217510223389</v>
       </c>
       <c r="H174" t="n">
         <v>7676566</v>
@@ -5560,7 +5560,7 @@
         <v>1.22699999809265</v>
       </c>
       <c r="G179" t="n">
-        <v>0.758490145206451</v>
+        <v>0.758490085601807</v>
       </c>
       <c r="H179" t="n">
         <v>17207944</v>
@@ -5647,7 +5647,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G182" t="n">
-        <v>0.765907943248749</v>
+        <v>0.765908002853394</v>
       </c>
       <c r="H182" t="n">
         <v>8005896</v>
@@ -5676,7 +5676,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G183" t="n">
-        <v>0.754781007766724</v>
+        <v>0.754780948162079</v>
       </c>
       <c r="H183" t="n">
         <v>9222204</v>
@@ -5705,7 +5705,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G184" t="n">
-        <v>0.765907943248749</v>
+        <v>0.765908002853394</v>
       </c>
       <c r="H184" t="n">
         <v>5718065</v>
@@ -5734,7 +5734,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>0.760344564914703</v>
+        <v>0.760344505310059</v>
       </c>
       <c r="H185" t="n">
         <v>6262111</v>
@@ -5763,7 +5763,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G186" t="n">
-        <v>0.762817203998566</v>
+        <v>0.76281726360321</v>
       </c>
       <c r="H186" t="n">
         <v>9472823</v>
@@ -5792,7 +5792,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G187" t="n">
-        <v>0.77332603931427</v>
+        <v>0.773326098918915</v>
       </c>
       <c r="H187" t="n">
         <v>8987270</v>
@@ -5821,7 +5821,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G188" t="n">
-        <v>0.768380641937256</v>
+        <v>0.768380761146545</v>
       </c>
       <c r="H188" t="n">
         <v>6115505</v>
@@ -5937,7 +5937,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G192" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H192" t="n">
         <v>10372420</v>
@@ -5966,7 +5966,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G193" t="n">
-        <v>0.777034997940063</v>
+        <v>0.777035057544708</v>
       </c>
       <c r="H193" t="n">
         <v>9567769</v>
@@ -6024,7 +6024,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G195" t="n">
-        <v>0.747363030910492</v>
+        <v>0.747363090515137</v>
       </c>
       <c r="H195" t="n">
         <v>11532257</v>
@@ -6111,7 +6111,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>0.754162788391113</v>
+        <v>0.754162847995758</v>
       </c>
       <c r="H198" t="n">
         <v>11765261</v>
@@ -6140,7 +6140,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G199" t="n">
-        <v>0.748599410057068</v>
+        <v>0.748599350452423</v>
       </c>
       <c r="H199" t="n">
         <v>11144497</v>
@@ -6169,7 +6169,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G200" t="n">
-        <v>0.752308309078217</v>
+        <v>0.752308368682861</v>
       </c>
       <c r="H200" t="n">
         <v>8867608</v>
@@ -6314,7 +6314,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H205" t="n">
         <v>8176110</v>
@@ -6372,7 +6372,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G207" t="n">
-        <v>0.789398312568665</v>
+        <v>0.789398372173309</v>
       </c>
       <c r="H207" t="n">
         <v>7716943</v>
@@ -6430,7 +6430,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G209" t="n">
-        <v>0.765907943248749</v>
+        <v>0.765908002853394</v>
       </c>
       <c r="H209" t="n">
         <v>8193662</v>
@@ -6488,7 +6488,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G211" t="n">
-        <v>0.764053344726562</v>
+        <v>0.764053404331207</v>
       </c>
       <c r="H211" t="n">
         <v>5758359</v>
@@ -6546,7 +6546,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G213" t="n">
-        <v>0.764053344726562</v>
+        <v>0.764053404331207</v>
       </c>
       <c r="H213" t="n">
         <v>6974084</v>
@@ -6575,7 +6575,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G214" t="n">
-        <v>0.767144441604614</v>
+        <v>0.767144322395325</v>
       </c>
       <c r="H214" t="n">
         <v>5837261</v>
@@ -6604,7 +6604,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G215" t="n">
-        <v>0.770235121250153</v>
+        <v>0.770235180854797</v>
       </c>
       <c r="H215" t="n">
         <v>6425613</v>
@@ -6633,7 +6633,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G216" t="n">
-        <v>0.749217450618744</v>
+        <v>0.749217510223389</v>
       </c>
       <c r="H216" t="n">
         <v>6950616</v>
@@ -6662,7 +6662,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G217" t="n">
-        <v>0.740563094615936</v>
+        <v>0.740563213825226</v>
       </c>
       <c r="H217" t="n">
         <v>7043433</v>
@@ -6691,7 +6691,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>0.726345300674438</v>
+        <v>0.726345360279083</v>
       </c>
       <c r="H218" t="n">
         <v>5526359</v>
@@ -6720,7 +6720,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G219" t="n">
-        <v>0.738708794116974</v>
+        <v>0.738708734512329</v>
       </c>
       <c r="H219" t="n">
         <v>6538446</v>
@@ -6836,7 +6836,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G223" t="n">
-        <v>0.702236950397491</v>
+        <v>0.702236890792847</v>
       </c>
       <c r="H223" t="n">
         <v>14866146</v>
@@ -6923,7 +6923,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G226" t="n">
-        <v>0.696673452854156</v>
+        <v>0.696673333644867</v>
       </c>
       <c r="H226" t="n">
         <v>12196110</v>
@@ -6952,7 +6952,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G227" t="n">
-        <v>0.686164557933807</v>
+        <v>0.686164498329163</v>
       </c>
       <c r="H227" t="n">
         <v>8524030</v>
@@ -7039,7 +7039,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G230" t="n">
-        <v>0.665146887302399</v>
+        <v>0.665147006511688</v>
       </c>
       <c r="H230" t="n">
         <v>9050922</v>
@@ -7097,7 +7097,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G232" t="n">
-        <v>0.681219279766083</v>
+        <v>0.681219220161438</v>
       </c>
       <c r="H232" t="n">
         <v>6682902</v>
@@ -7126,7 +7126,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G233" t="n">
-        <v>0.679364681243896</v>
+        <v>0.679364621639252</v>
       </c>
       <c r="H233" t="n">
         <v>3943772</v>
@@ -7155,7 +7155,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G234" t="n">
-        <v>0.675037562847137</v>
+        <v>0.675037503242493</v>
       </c>
       <c r="H234" t="n">
         <v>7594797</v>
@@ -7300,7 +7300,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G239" t="n">
-        <v>0.686164557933807</v>
+        <v>0.686164498329163</v>
       </c>
       <c r="H239" t="n">
         <v>11936959</v>
@@ -7358,7 +7358,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>0.720163643360138</v>
+        <v>0.720163702964783</v>
       </c>
       <c r="H241" t="n">
         <v>16590579</v>
@@ -7445,7 +7445,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G244" t="n">
-        <v>0.736236035823822</v>
+        <v>0.736235976219177</v>
       </c>
       <c r="H244" t="n">
         <v>7415048</v>
@@ -7677,7 +7677,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G252" t="n">
-        <v>0.727581799030304</v>
+        <v>0.727581679821014</v>
       </c>
       <c r="H252" t="n">
         <v>8162970</v>
@@ -7735,7 +7735,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G254" t="n">
-        <v>0.751072108745575</v>
+        <v>0.751071989536285</v>
       </c>
       <c r="H254" t="n">
         <v>5034388</v>
@@ -7822,7 +7822,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>0.760344564914703</v>
+        <v>0.760344505310059</v>
       </c>
       <c r="H257" t="n">
         <v>5374288</v>
@@ -7851,7 +7851,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G258" t="n">
-        <v>0.780125677585602</v>
+        <v>0.780125796794891</v>
       </c>
       <c r="H258" t="n">
         <v>10979509</v>
@@ -7909,7 +7909,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G260" t="n">
-        <v>0.78445303440094</v>
+        <v>0.78445291519165</v>
       </c>
       <c r="H260" t="n">
         <v>11785309</v>
@@ -7938,7 +7938,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G261" t="n">
-        <v>0.781980395317078</v>
+        <v>0.781980216503143</v>
       </c>
       <c r="H261" t="n">
         <v>8754392</v>
@@ -7996,7 +7996,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G263" t="n">
-        <v>0.767144441604614</v>
+        <v>0.767144322395325</v>
       </c>
       <c r="H263" t="n">
         <v>9548075</v>
@@ -8083,7 +8083,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G266" t="n">
-        <v>0.786925554275513</v>
+        <v>0.786925613880157</v>
       </c>
       <c r="H266" t="n">
         <v>10106082</v>
@@ -8141,7 +8141,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G268" t="n">
-        <v>0.793725430965424</v>
+        <v>0.793725490570068</v>
       </c>
       <c r="H268" t="n">
         <v>12851795</v>
@@ -8199,7 +8199,7 @@
         <v>1.29700005054474</v>
       </c>
       <c r="G270" t="n">
-        <v>0.801761627197266</v>
+        <v>0.801761746406555</v>
       </c>
       <c r="H270" t="n">
         <v>8440213</v>
@@ -8228,7 +8228,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>0.809797763824463</v>
+        <v>0.809797704219818</v>
       </c>
       <c r="H271" t="n">
         <v>10589102</v>
@@ -8373,7 +8373,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G276" t="n">
-        <v>0.786925554275513</v>
+        <v>0.786925613880157</v>
       </c>
       <c r="H276" t="n">
         <v>4506909</v>
@@ -8402,7 +8402,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>0.778889536857605</v>
+        <v>0.778889358043671</v>
       </c>
       <c r="H277" t="n">
         <v>7416415</v>
@@ -8460,7 +8460,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G279" t="n">
-        <v>0.762817203998566</v>
+        <v>0.76281726360321</v>
       </c>
       <c r="H279" t="n">
         <v>14022527</v>
@@ -8576,7 +8576,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G283" t="n">
-        <v>0.769617021083832</v>
+        <v>0.769617080688477</v>
       </c>
       <c r="H283" t="n">
         <v>9057541</v>
@@ -8692,7 +8692,7 @@
         <v>1.30299997329712</v>
       </c>
       <c r="G287" t="n">
-        <v>0.805470645427704</v>
+        <v>0.80547046661377</v>
       </c>
       <c r="H287" t="n">
         <v>8457206</v>
@@ -8721,7 +8721,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G288" t="n">
-        <v>0.799288928508759</v>
+        <v>0.799288868904114</v>
       </c>
       <c r="H288" t="n">
         <v>11633913</v>
@@ -8779,7 +8779,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>0.783834755420685</v>
+        <v>0.78383481502533</v>
       </c>
       <c r="H290" t="n">
         <v>15671854</v>
@@ -8808,7 +8808,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G291" t="n">
-        <v>0.79063481092453</v>
+        <v>0.79063469171524</v>
       </c>
       <c r="H291" t="n">
         <v>8140674</v>
@@ -8837,7 +8837,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G292" t="n">
-        <v>0.788161993026733</v>
+        <v>0.788161933422089</v>
       </c>
       <c r="H292" t="n">
         <v>5614191</v>
@@ -8866,7 +8866,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G293" t="n">
-        <v>0.785071194171906</v>
+        <v>0.78507125377655</v>
       </c>
       <c r="H293" t="n">
         <v>4008191</v>
@@ -8895,7 +8895,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G294" t="n">
-        <v>0.791252851486206</v>
+        <v>0.791252791881561</v>
       </c>
       <c r="H294" t="n">
         <v>13995917</v>
@@ -8924,7 +8924,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G295" t="n">
-        <v>0.79063481092453</v>
+        <v>0.79063469171524</v>
       </c>
       <c r="H295" t="n">
         <v>7728394</v>
@@ -8982,7 +8982,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>0.788161993026733</v>
+        <v>0.788161933422089</v>
       </c>
       <c r="H297" t="n">
         <v>8827651</v>
@@ -9011,7 +9011,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G298" t="n">
-        <v>0.807943224906921</v>
+        <v>0.807943344116211</v>
       </c>
       <c r="H298" t="n">
         <v>10672327</v>
@@ -9040,7 +9040,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G299" t="n">
-        <v>0.810416042804718</v>
+        <v>0.810415923595428</v>
       </c>
       <c r="H299" t="n">
         <v>18126230</v>
@@ -9069,7 +9069,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G300" t="n">
-        <v>0.825252056121826</v>
+        <v>0.825251996517181</v>
       </c>
       <c r="H300" t="n">
         <v>17117579</v>
@@ -9127,7 +9127,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G302" t="n">
-        <v>0.828342854976654</v>
+        <v>0.828342795372009</v>
       </c>
       <c r="H302" t="n">
         <v>13033350</v>
@@ -9214,7 +9214,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G305" t="n">
-        <v>0.825870096683502</v>
+        <v>0.825870037078857</v>
       </c>
       <c r="H305" t="n">
         <v>9363360</v>
@@ -9243,7 +9243,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G306" t="n">
-        <v>0.827106416225433</v>
+        <v>0.827106475830078</v>
       </c>
       <c r="H306" t="n">
         <v>7694519</v>
@@ -9272,7 +9272,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G307" t="n">
-        <v>0.814125001430511</v>
+        <v>0.814124941825867</v>
       </c>
       <c r="H307" t="n">
         <v>7503436</v>
@@ -9330,7 +9330,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>0.819070339202881</v>
+        <v>0.819070279598236</v>
       </c>
       <c r="H309" t="n">
         <v>13399119</v>
@@ -9388,7 +9388,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G311" t="n">
-        <v>0.832670032978058</v>
+        <v>0.832669913768768</v>
       </c>
       <c r="H311" t="n">
         <v>9299588</v>
@@ -9417,7 +9417,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G312" t="n">
-        <v>0.834524512290955</v>
+        <v>0.834524393081665</v>
       </c>
       <c r="H312" t="n">
         <v>15364137</v>
@@ -9446,7 +9446,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G313" t="n">
-        <v>0.8468878865242</v>
+        <v>0.846887826919556</v>
       </c>
       <c r="H313" t="n">
         <v>11370290</v>
@@ -9475,7 +9475,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G314" t="n">
-        <v>0.853069484233856</v>
+        <v>0.853069543838501</v>
       </c>
       <c r="H314" t="n">
         <v>9518568</v>
@@ -9562,7 +9562,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G317" t="n">
-        <v>0.867905616760254</v>
+        <v>0.86790543794632</v>
       </c>
       <c r="H317" t="n">
         <v>7200691</v>
@@ -9591,7 +9591,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G318" t="n">
-        <v>0.866669058799744</v>
+        <v>0.866668999195099</v>
       </c>
       <c r="H318" t="n">
         <v>6255254</v>
@@ -9649,7 +9649,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G320" t="n">
-        <v>0.876559793949127</v>
+        <v>0.876559734344482</v>
       </c>
       <c r="H320" t="n">
         <v>8476463</v>
@@ -9707,7 +9707,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G322" t="n">
-        <v>0.876559793949127</v>
+        <v>0.876559734344482</v>
       </c>
       <c r="H322" t="n">
         <v>11178772</v>
@@ -9736,7 +9736,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>0.853069484233856</v>
+        <v>0.853069543838501</v>
       </c>
       <c r="H323" t="n">
         <v>29031819</v>
@@ -9794,7 +9794,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G325" t="n">
-        <v>0.835760831832886</v>
+        <v>0.835760891437531</v>
       </c>
       <c r="H325" t="n">
         <v>13883820</v>
@@ -9823,7 +9823,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>0.837615311145782</v>
+        <v>0.837615191936493</v>
       </c>
       <c r="H326" t="n">
         <v>12794596</v>
@@ -9852,7 +9852,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G327" t="n">
-        <v>0.851215004920959</v>
+        <v>0.85121488571167</v>
       </c>
       <c r="H327" t="n">
         <v>10214345</v>
@@ -9881,7 +9881,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G328" t="n">
-        <v>0.844415307044983</v>
+        <v>0.844415247440338</v>
       </c>
       <c r="H328" t="n">
         <v>8501936</v>
@@ -9910,7 +9910,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G329" t="n">
-        <v>0.854305863380432</v>
+        <v>0.854305684566498</v>
       </c>
       <c r="H329" t="n">
         <v>9046198</v>
@@ -9968,7 +9968,7 @@
         <v>1.35300004482269</v>
       </c>
       <c r="G331" t="n">
-        <v>0.836378991603851</v>
+        <v>0.836379051208496</v>
       </c>
       <c r="H331" t="n">
         <v>8369238</v>
@@ -10026,7 +10026,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G333" t="n">
-        <v>0.828342854976654</v>
+        <v>0.828342795372009</v>
       </c>
       <c r="H333" t="n">
         <v>6636552</v>
@@ -10055,7 +10055,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G334" t="n">
-        <v>0.817215859889984</v>
+        <v>0.817215800285339</v>
       </c>
       <c r="H334" t="n">
         <v>4410618</v>
@@ -10084,7 +10084,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>0.825252056121826</v>
+        <v>0.825251996517181</v>
       </c>
       <c r="H335" t="n">
         <v>6577104</v>
@@ -10113,7 +10113,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G336" t="n">
-        <v>0.841942369937897</v>
+        <v>0.841942310333252</v>
       </c>
       <c r="H336" t="n">
         <v>14036173</v>
@@ -10142,7 +10142,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G337" t="n">
-        <v>0.851215004920959</v>
+        <v>0.85121488571167</v>
       </c>
       <c r="H337" t="n">
         <v>6505623</v>
@@ -10200,7 +10200,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G339" t="n">
-        <v>0.851215004920959</v>
+        <v>0.85121488571167</v>
       </c>
       <c r="H339" t="n">
         <v>10543690</v>
@@ -10258,7 +10258,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G341" t="n">
-        <v>0.858014762401581</v>
+        <v>0.858014702796936</v>
       </c>
       <c r="H341" t="n">
         <v>8506992</v>
@@ -10316,7 +10316,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G343" t="n">
-        <v>0.88459587097168</v>
+        <v>0.884595930576324</v>
       </c>
       <c r="H343" t="n">
         <v>15206663</v>
@@ -10403,7 +10403,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G346" t="n">
-        <v>0.875323414802551</v>
+        <v>0.875323474407196</v>
       </c>
       <c r="H346" t="n">
         <v>9141532</v>
@@ -10461,7 +10461,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G348" t="n">
-        <v>0.914267838001251</v>
+        <v>0.914267957210541</v>
       </c>
       <c r="H348" t="n">
         <v>19810342</v>
@@ -10490,7 +10490,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G349" t="n">
-        <v>0.921067833900452</v>
+        <v>0.921067774295807</v>
       </c>
       <c r="H349" t="n">
         <v>23074131</v>
@@ -10519,7 +10519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G350" t="n">
-        <v>0.917358815670013</v>
+        <v>0.917358756065369</v>
       </c>
       <c r="H350" t="n">
         <v>16538119</v>
@@ -10548,7 +10548,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G351" t="n">
-        <v>0.919213175773621</v>
+        <v>0.91921329498291</v>
       </c>
       <c r="H351" t="n">
         <v>14520469</v>
@@ -10577,7 +10577,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G352" t="n">
-        <v>0.898813784122467</v>
+        <v>0.898813724517822</v>
       </c>
       <c r="H352" t="n">
         <v>11623550</v>
@@ -10635,7 +10635,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G354" t="n">
-        <v>0.914886116981506</v>
+        <v>0.914886176586151</v>
       </c>
       <c r="H354" t="n">
         <v>13675287</v>
@@ -10664,7 +10664,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G355" t="n">
-        <v>0.937393844127655</v>
+        <v>0.937393724918365</v>
       </c>
       <c r="H355" t="n">
         <v>13261526</v>
@@ -10693,7 +10693,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>0.94314843416214</v>
+        <v>0.943148553371429</v>
       </c>
       <c r="H356" t="n">
         <v>8057549</v>
@@ -10751,7 +10751,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G358" t="n">
-        <v>0.954658269882202</v>
+        <v>0.954658150672913</v>
       </c>
       <c r="H358" t="n">
         <v>12660084</v>
@@ -10780,7 +10780,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>0.947624444961548</v>
+        <v>0.947624385356903</v>
       </c>
       <c r="H359" t="n">
         <v>8749661</v>
@@ -10838,7 +10838,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G361" t="n">
-        <v>0.93675434589386</v>
+        <v>0.936754405498505</v>
       </c>
       <c r="H361" t="n">
         <v>8371662</v>
@@ -10896,7 +10896,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G363" t="n">
-        <v>0.943787932395935</v>
+        <v>0.94378787279129</v>
       </c>
       <c r="H363" t="n">
         <v>8138057</v>
@@ -10954,7 +10954,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G365" t="n">
-        <v>0.93036013841629</v>
+        <v>0.930360019207001</v>
       </c>
       <c r="H365" t="n">
         <v>5912949</v>
@@ -10983,7 +10983,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G366" t="n">
-        <v>0.947624444961548</v>
+        <v>0.947624385356903</v>
       </c>
       <c r="H366" t="n">
         <v>7517747</v>
@@ -11128,7 +11128,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G371" t="n">
-        <v>0.947624444961548</v>
+        <v>0.947624385356903</v>
       </c>
       <c r="H371" t="n">
         <v>10918022</v>
@@ -11186,7 +11186,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G373" t="n">
-        <v>0.955936968326569</v>
+        <v>0.955937087535858</v>
       </c>
       <c r="H373" t="n">
         <v>12471585</v>
@@ -11215,7 +11215,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G374" t="n">
-        <v>0.954658269882202</v>
+        <v>0.954658150672913</v>
       </c>
       <c r="H374" t="n">
         <v>10314464</v>
@@ -11273,7 +11273,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G376" t="n">
-        <v>0.961052477359772</v>
+        <v>0.961052358150482</v>
       </c>
       <c r="H376" t="n">
         <v>8884843</v>
@@ -11331,7 +11331,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G378" t="n">
-        <v>0.982792794704437</v>
+        <v>0.982792675495148</v>
       </c>
       <c r="H378" t="n">
         <v>12750291</v>
@@ -11418,7 +11418,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G381" t="n">
-        <v>0.949542760848999</v>
+        <v>0.949542939662933</v>
       </c>
       <c r="H381" t="n">
         <v>10695460</v>
@@ -11476,7 +11476,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G383" t="n">
-        <v>0.932278335094452</v>
+        <v>0.932278454303741</v>
       </c>
       <c r="H383" t="n">
         <v>11826675</v>
@@ -11505,7 +11505,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>0.92972069978714</v>
+        <v>0.929720640182495</v>
       </c>
       <c r="H384" t="n">
         <v>6857793</v>
@@ -11534,7 +11534,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G385" t="n">
-        <v>0.925884187221527</v>
+        <v>0.925884008407593</v>
       </c>
       <c r="H385" t="n">
         <v>6224262</v>
@@ -11563,7 +11563,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>0.921408236026764</v>
+        <v>0.92140805721283</v>
       </c>
       <c r="H386" t="n">
         <v>5500264</v>
@@ -11592,7 +11592,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G387" t="n">
-        <v>0.92972069978714</v>
+        <v>0.929720640182495</v>
       </c>
       <c r="H387" t="n">
         <v>5035527</v>
@@ -11679,7 +11679,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G390" t="n">
-        <v>0.925884187221527</v>
+        <v>0.925884008407593</v>
       </c>
       <c r="H390" t="n">
         <v>8054087</v>
@@ -11708,7 +11708,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G391" t="n">
-        <v>0.920129418373108</v>
+        <v>0.920129358768463</v>
       </c>
       <c r="H391" t="n">
         <v>7356510</v>
@@ -11737,7 +11737,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G392" t="n">
-        <v>0.935475468635559</v>
+        <v>0.935475587844849</v>
       </c>
       <c r="H392" t="n">
         <v>6555015</v>
@@ -11766,7 +11766,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G393" t="n">
-        <v>0.934196710586548</v>
+        <v>0.934196591377258</v>
       </c>
       <c r="H393" t="n">
         <v>6760149</v>
@@ -11795,7 +11795,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G394" t="n">
-        <v>0.939951479434967</v>
+        <v>0.939951539039612</v>
       </c>
       <c r="H394" t="n">
         <v>5987751</v>
@@ -11824,7 +11824,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G395" t="n">
-        <v>0.928441762924194</v>
+        <v>0.928441882133484</v>
       </c>
       <c r="H395" t="n">
         <v>11697163</v>
@@ -11853,7 +11853,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G396" t="n">
-        <v>0.916292786598206</v>
+        <v>0.916292905807495</v>
       </c>
       <c r="H396" t="n">
         <v>15809057</v>
@@ -11882,7 +11882,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G397" t="n">
-        <v>0.915013909339905</v>
+        <v>0.915014028549194</v>
       </c>
       <c r="H397" t="n">
         <v>10301025</v>
@@ -11911,7 +11911,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G398" t="n">
-        <v>0.916292786598206</v>
+        <v>0.916292905807495</v>
       </c>
       <c r="H398" t="n">
         <v>16886128</v>
@@ -11940,7 +11940,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G399" t="n">
-        <v>0.907980382442474</v>
+        <v>0.907980263233185</v>
       </c>
       <c r="H399" t="n">
         <v>6790051</v>
@@ -11969,7 +11969,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G400" t="n">
-        <v>0.911816656589508</v>
+        <v>0.911816835403442</v>
       </c>
       <c r="H400" t="n">
         <v>5787207</v>
@@ -12056,7 +12056,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G403" t="n">
-        <v>0.919489860534668</v>
+        <v>0.919489800930023</v>
       </c>
       <c r="H403" t="n">
         <v>4512530</v>
@@ -12085,7 +12085,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G404" t="n">
-        <v>0.906701385974884</v>
+        <v>0.906701445579529</v>
       </c>
       <c r="H404" t="n">
         <v>22358659</v>
@@ -12114,7 +12114,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G405" t="n">
-        <v>0.919489860534668</v>
+        <v>0.919489800930023</v>
       </c>
       <c r="H405" t="n">
         <v>13566198</v>
@@ -12143,7 +12143,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G406" t="n">
-        <v>0.915013909339905</v>
+        <v>0.915014028549194</v>
       </c>
       <c r="H406" t="n">
         <v>7255916</v>
@@ -12172,7 +12172,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G407" t="n">
-        <v>0.909898459911346</v>
+        <v>0.909898638725281</v>
       </c>
       <c r="H407" t="n">
         <v>5228922</v>
@@ -12201,7 +12201,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G408" t="n">
-        <v>0.913095772266388</v>
+        <v>0.913095653057098</v>
       </c>
       <c r="H408" t="n">
         <v>8735341</v>
@@ -12259,7 +12259,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G410" t="n">
-        <v>0.909259259700775</v>
+        <v>0.909259140491486</v>
       </c>
       <c r="H410" t="n">
         <v>3622567</v>
@@ -12288,7 +12288,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G411" t="n">
-        <v>0.918210983276367</v>
+        <v>0.918211102485657</v>
       </c>
       <c r="H411" t="n">
         <v>7858773</v>
@@ -12317,7 +12317,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G412" t="n">
-        <v>0.909898459911346</v>
+        <v>0.909898638725281</v>
       </c>
       <c r="H412" t="n">
         <v>5781280</v>
@@ -12346,7 +12346,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G413" t="n">
-        <v>0.901586055755615</v>
+        <v>0.90158599615097</v>
       </c>
       <c r="H413" t="n">
         <v>5960830</v>
@@ -12375,7 +12375,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G414" t="n">
-        <v>0.888797760009766</v>
+        <v>0.888797640800476</v>
       </c>
       <c r="H414" t="n">
         <v>8443255</v>
@@ -12404,7 +12404,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>0.904783189296722</v>
+        <v>0.904783308506012</v>
       </c>
       <c r="H415" t="n">
         <v>7045240</v>
@@ -12462,7 +12462,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G417" t="n">
-        <v>0.910538017749786</v>
+        <v>0.910538077354431</v>
       </c>
       <c r="H417" t="n">
         <v>4077401</v>
@@ -12491,7 +12491,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G418" t="n">
-        <v>0.913735151290894</v>
+        <v>0.913735210895538</v>
       </c>
       <c r="H418" t="n">
         <v>4270095</v>
@@ -12520,7 +12520,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G419" t="n">
-        <v>0.907980382442474</v>
+        <v>0.907980263233185</v>
       </c>
       <c r="H419" t="n">
         <v>3759684</v>
@@ -12549,7 +12549,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G420" t="n">
-        <v>0.901586055755615</v>
+        <v>0.90158599615097</v>
       </c>
       <c r="H420" t="n">
         <v>5701739</v>
@@ -12578,7 +12578,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G421" t="n">
-        <v>0.896470665931702</v>
+        <v>0.896470606327057</v>
       </c>
       <c r="H421" t="n">
         <v>4846491</v>
@@ -12607,7 +12607,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G422" t="n">
-        <v>0.903504312038422</v>
+        <v>0.903504371643066</v>
       </c>
       <c r="H422" t="n">
         <v>5833467</v>
@@ -12636,7 +12636,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>0.891994833946228</v>
+        <v>0.891994774341583</v>
       </c>
       <c r="H423" t="n">
         <v>6400043</v>
@@ -12665,7 +12665,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G424" t="n">
-        <v>0.886239945888519</v>
+        <v>0.886240005493164</v>
       </c>
       <c r="H424" t="n">
         <v>5116170</v>
@@ -12694,7 +12694,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G425" t="n">
-        <v>0.882403433322906</v>
+        <v>0.882403492927551</v>
       </c>
       <c r="H425" t="n">
         <v>5525455</v>
@@ -12723,7 +12723,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G426" t="n">
-        <v>0.890076339244843</v>
+        <v>0.890076398849487</v>
       </c>
       <c r="H426" t="n">
         <v>7920589</v>
@@ -12752,7 +12752,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G427" t="n">
-        <v>0.90222555398941</v>
+        <v>0.902225494384766</v>
       </c>
       <c r="H427" t="n">
         <v>9474897</v>
@@ -12810,7 +12810,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G429" t="n">
-        <v>0.907980382442474</v>
+        <v>0.907980263233185</v>
       </c>
       <c r="H429" t="n">
         <v>4922374</v>
@@ -12839,7 +12839,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G430" t="n">
-        <v>0.909259259700775</v>
+        <v>0.909259140491486</v>
       </c>
       <c r="H430" t="n">
         <v>7292532</v>
@@ -12868,7 +12868,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G431" t="n">
-        <v>0.92908126115799</v>
+        <v>0.929081201553345</v>
       </c>
       <c r="H431" t="n">
         <v>12761120</v>
@@ -12897,7 +12897,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>0.933557152748108</v>
+        <v>0.933557212352753</v>
       </c>
       <c r="H432" t="n">
         <v>10000925</v>
@@ -12926,7 +12926,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G433" t="n">
-        <v>0.943787932395935</v>
+        <v>0.94378787279129</v>
       </c>
       <c r="H433" t="n">
         <v>13640021</v>
@@ -13013,7 +13013,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>0.947624444961548</v>
+        <v>0.947624385356903</v>
       </c>
       <c r="H436" t="n">
         <v>14736166</v>
@@ -13071,7 +13071,7 @@
         <v>1.46899998188019</v>
       </c>
       <c r="G438" t="n">
-        <v>0.939311981201172</v>
+        <v>0.939311921596527</v>
       </c>
       <c r="H438" t="n">
         <v>31570151</v>
@@ -13158,7 +13158,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G441" t="n">
-        <v>0.935475468635559</v>
+        <v>0.935475587844849</v>
       </c>
       <c r="H441" t="n">
         <v>6407717</v>
@@ -13187,7 +13187,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G442" t="n">
-        <v>0.92908126115799</v>
+        <v>0.929081201553345</v>
       </c>
       <c r="H442" t="n">
         <v>9555700</v>
@@ -13216,7 +13216,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G443" t="n">
-        <v>0.932278335094452</v>
+        <v>0.932278454303741</v>
       </c>
       <c r="H443" t="n">
         <v>6291914</v>
@@ -13245,7 +13245,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G444" t="n">
-        <v>0.928441762924194</v>
+        <v>0.928441882133484</v>
       </c>
       <c r="H444" t="n">
         <v>8624455</v>
@@ -13303,7 +13303,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G446" t="n">
-        <v>0.948903441429138</v>
+        <v>0.948903381824493</v>
       </c>
       <c r="H446" t="n">
         <v>10128657</v>
@@ -13361,7 +13361,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G448" t="n">
-        <v>0.93036013841629</v>
+        <v>0.930360019207001</v>
       </c>
       <c r="H448" t="n">
         <v>12316190</v>
@@ -13419,7 +13419,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G450" t="n">
-        <v>0.937393844127655</v>
+        <v>0.937393724918365</v>
       </c>
       <c r="H450" t="n">
         <v>7348786</v>
@@ -13448,7 +13448,7 @@
         <v>1.45099997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>0.927802383899689</v>
+        <v>0.927802324295044</v>
       </c>
       <c r="H451" t="n">
         <v>10342253</v>
@@ -13477,7 +13477,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G452" t="n">
-        <v>0.920129418373108</v>
+        <v>0.920129358768463</v>
       </c>
       <c r="H452" t="n">
         <v>16753987</v>
@@ -13506,7 +13506,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G453" t="n">
-        <v>0.903504312038422</v>
+        <v>0.903504371643066</v>
       </c>
       <c r="H453" t="n">
         <v>8344202</v>
@@ -13593,7 +13593,7 @@
         <v>1.43299996852875</v>
       </c>
       <c r="G456" t="n">
-        <v>0.916292786598206</v>
+        <v>0.916292905807495</v>
       </c>
       <c r="H456" t="n">
         <v>9644379</v>
@@ -13680,7 +13680,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G459" t="n">
-        <v>0.918210983276367</v>
+        <v>0.918211102485657</v>
       </c>
       <c r="H459" t="n">
         <v>6604044</v>
@@ -13709,7 +13709,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G460" t="n">
-        <v>0.925244867801666</v>
+        <v>0.925244748592377</v>
       </c>
       <c r="H460" t="n">
         <v>8601837</v>
@@ -13738,7 +13738,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G461" t="n">
-        <v>0.924605250358582</v>
+        <v>0.924605190753937</v>
       </c>
       <c r="H461" t="n">
         <v>6464385</v>
@@ -13796,7 +13796,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G463" t="n">
-        <v>0.927162945270538</v>
+        <v>0.927163064479828</v>
       </c>
       <c r="H463" t="n">
         <v>6965687</v>
@@ -13825,7 +13825,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G464" t="n">
-        <v>0.918210983276367</v>
+        <v>0.918211102485657</v>
       </c>
       <c r="H464" t="n">
         <v>5394603</v>
@@ -13854,7 +13854,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G465" t="n">
-        <v>0.918210983276367</v>
+        <v>0.918211102485657</v>
       </c>
       <c r="H465" t="n">
         <v>10672531</v>
@@ -13912,7 +13912,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G467" t="n">
-        <v>0.906701385974884</v>
+        <v>0.906701445579529</v>
       </c>
       <c r="H467" t="n">
         <v>14956822</v>
@@ -13941,7 +13941,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G468" t="n">
-        <v>0.925884187221527</v>
+        <v>0.925884008407593</v>
       </c>
       <c r="H468" t="n">
         <v>12048450</v>
@@ -13970,7 +13970,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G469" t="n">
-        <v>0.928441762924194</v>
+        <v>0.928441882133484</v>
       </c>
       <c r="H469" t="n">
         <v>5061910</v>
@@ -13999,7 +13999,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G470" t="n">
-        <v>0.94314843416214</v>
+        <v>0.943148553371429</v>
       </c>
       <c r="H470" t="n">
         <v>12675927</v>
@@ -14057,7 +14057,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G472" t="n">
-        <v>0.95018208026886</v>
+        <v>0.950182199478149</v>
       </c>
       <c r="H472" t="n">
         <v>6083909</v>
@@ -14144,7 +14144,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G475" t="n">
-        <v>0.946985065937042</v>
+        <v>0.946985006332397</v>
       </c>
       <c r="H475" t="n">
         <v>8161831</v>
@@ -14173,7 +14173,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G476" t="n">
-        <v>0.94314843416214</v>
+        <v>0.943148553371429</v>
       </c>
       <c r="H476" t="n">
         <v>10553829</v>
@@ -14202,7 +14202,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G477" t="n">
-        <v>0.92972069978714</v>
+        <v>0.929720640182495</v>
       </c>
       <c r="H477" t="n">
         <v>8623358</v>
@@ -14231,7 +14231,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G478" t="n">
-        <v>0.92972069978714</v>
+        <v>0.929720640182495</v>
       </c>
       <c r="H478" t="n">
         <v>7350204</v>
@@ -14260,7 +14260,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G479" t="n">
-        <v>0.922687113285065</v>
+        <v>0.92268705368042</v>
       </c>
       <c r="H479" t="n">
         <v>10051356</v>
@@ -14289,7 +14289,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G480" t="n">
-        <v>0.974480152130127</v>
+        <v>0.974480271339417</v>
       </c>
       <c r="H480" t="n">
         <v>36413380</v>
@@ -14347,7 +14347,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G482" t="n">
-        <v>0.968086063861847</v>
+        <v>0.968086183071136</v>
       </c>
       <c r="H482" t="n">
         <v>13965573</v>
@@ -14405,7 +14405,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G484" t="n">
-        <v>0.977037906646729</v>
+        <v>0.977038025856018</v>
       </c>
       <c r="H484" t="n">
         <v>9851541</v>
@@ -14463,7 +14463,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G486" t="n">
-        <v>0.9859898686409</v>
+        <v>0.985989987850189</v>
       </c>
       <c r="H486" t="n">
         <v>8630178</v>
@@ -14492,7 +14492,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G487" t="n">
-        <v>0.982792794704437</v>
+        <v>0.982792675495148</v>
       </c>
       <c r="H487" t="n">
         <v>6943861</v>
@@ -14521,7 +14521,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G488" t="n">
-        <v>0.991744756698608</v>
+        <v>0.991744637489319</v>
       </c>
       <c r="H488" t="n">
         <v>7287798</v>
@@ -14579,7 +14579,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G490" t="n">
-        <v>0.991744756698608</v>
+        <v>0.991744637489319</v>
       </c>
       <c r="H490" t="n">
         <v>7498614</v>
@@ -14666,7 +14666,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G493" t="n">
-        <v>0.996860265731812</v>
+        <v>0.996860146522522</v>
       </c>
       <c r="H493" t="n">
         <v>7249624</v>
@@ -14695,7 +14695,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G494" t="n">
-        <v>1.00517272949219</v>
+        <v>1.0051726102829</v>
       </c>
       <c r="H494" t="n">
         <v>5946618</v>
@@ -14753,7 +14753,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G496" t="n">
-        <v>1.0237158536911</v>
+        <v>1.02371573448181</v>
       </c>
       <c r="H496" t="n">
         <v>9155645</v>
@@ -14782,7 +14782,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03650450706482</v>
+        <v>1.03650438785553</v>
       </c>
       <c r="H497" t="n">
         <v>11000958</v>
@@ -14840,7 +14840,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03394675254822</v>
+        <v>1.03394651412964</v>
       </c>
       <c r="H499" t="n">
         <v>7487510</v>
@@ -14869,7 +14869,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03266787528992</v>
+        <v>1.03266775608063</v>
       </c>
       <c r="H500" t="n">
         <v>11007587</v>
@@ -14898,7 +14898,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G501" t="n">
-        <v>1.00581192970276</v>
+        <v>1.00581181049347</v>
       </c>
       <c r="H501" t="n">
         <v>10752353</v>
@@ -14927,7 +14927,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G502" t="n">
-        <v>0.996860265731812</v>
+        <v>0.996860146522522</v>
       </c>
       <c r="H502" t="n">
         <v>6821723</v>
@@ -14985,7 +14985,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G504" t="n">
-        <v>1.01156687736511</v>
+        <v>1.01156675815582</v>
       </c>
       <c r="H504" t="n">
         <v>9895448</v>
@@ -15014,7 +15014,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G505" t="n">
-        <v>0.996220529079437</v>
+        <v>0.996220648288727</v>
       </c>
       <c r="H505" t="n">
         <v>8481420</v>
@@ -15043,7 +15043,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G506" t="n">
-        <v>1.00069653987885</v>
+        <v>1.00069642066956</v>
       </c>
       <c r="H506" t="n">
         <v>7443479</v>
@@ -15072,7 +15072,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G507" t="n">
-        <v>0.998778283596039</v>
+        <v>0.998778402805328</v>
       </c>
       <c r="H507" t="n">
         <v>5098195</v>
@@ -15188,7 +15188,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G511" t="n">
-        <v>0.9859898686409</v>
+        <v>0.985989987850189</v>
       </c>
       <c r="H511" t="n">
         <v>6318147</v>
@@ -15217,7 +15217,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G512" t="n">
-        <v>0.97320157289505</v>
+        <v>0.97320145368576</v>
       </c>
       <c r="H512" t="n">
         <v>8064937</v>
@@ -15246,7 +15246,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G513" t="n">
-        <v>0.969364762306213</v>
+        <v>0.969364881515503</v>
       </c>
       <c r="H513" t="n">
         <v>8323296</v>
@@ -15275,7 +15275,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G514" t="n">
-        <v>1.00389361381531</v>
+        <v>1.0038937330246</v>
       </c>
       <c r="H514" t="n">
         <v>13710193</v>
@@ -15333,7 +15333,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G516" t="n">
-        <v>1.01732170581818</v>
+        <v>1.01732158660889</v>
       </c>
       <c r="H516" t="n">
         <v>4094274</v>
@@ -15362,7 +15362,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G517" t="n">
-        <v>1.00581192970276</v>
+        <v>1.00581181049347</v>
       </c>
       <c r="H517" t="n">
         <v>8065526</v>
@@ -15391,7 +15391,7 @@
         <v>1.52900004386902</v>
       </c>
       <c r="G518" t="n">
-        <v>0.977677404880524</v>
+        <v>0.977677464485168</v>
       </c>
       <c r="H518" t="n">
         <v>12176563</v>
@@ -15420,7 +15420,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>0.971922516822815</v>
+        <v>0.971922636032104</v>
       </c>
       <c r="H519" t="n">
         <v>14917186</v>
@@ -15449,7 +15449,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G520" t="n">
-        <v>0.97320157289505</v>
+        <v>0.97320145368576</v>
       </c>
       <c r="H520" t="n">
         <v>7269009</v>
@@ -15478,7 +15478,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G521" t="n">
-        <v>0.980874598026276</v>
+        <v>0.980874717235565</v>
       </c>
       <c r="H521" t="n">
         <v>6946631</v>
@@ -15536,7 +15536,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G523" t="n">
-        <v>1.00836956501007</v>
+        <v>1.00836980342865</v>
       </c>
       <c r="H523" t="n">
         <v>16952015</v>
@@ -15565,7 +15565,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.00389361381531</v>
+        <v>1.0038937330246</v>
       </c>
       <c r="H524" t="n">
         <v>6922348</v>
@@ -15594,7 +15594,7 @@
         <v>1.58399999141693</v>
       </c>
       <c r="G525" t="n">
-        <v>1.01284551620483</v>
+        <v>1.01284575462341</v>
       </c>
       <c r="H525" t="n">
         <v>11677012</v>
@@ -15739,7 +15739,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G530" t="n">
-        <v>1.00517272949219</v>
+        <v>1.0051726102829</v>
       </c>
       <c r="H530" t="n">
         <v>6878276</v>
@@ -15797,7 +15797,7 @@
         <v>1.53250002861023</v>
       </c>
       <c r="G532" t="n">
-        <v>0.979915380477905</v>
+        <v>0.979915261268616</v>
       </c>
       <c r="H532" t="n">
         <v>10558300</v>
@@ -15826,7 +15826,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G533" t="n">
-        <v>0.988547623157501</v>
+        <v>0.988547503948212</v>
       </c>
       <c r="H533" t="n">
         <v>7915470</v>
@@ -15855,7 +15855,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G534" t="n">
-        <v>0.99430239200592</v>
+        <v>0.994302272796631</v>
       </c>
       <c r="H534" t="n">
         <v>9913089</v>
@@ -15884,7 +15884,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>0.971922516822815</v>
+        <v>0.971922636032104</v>
       </c>
       <c r="H535" t="n">
         <v>7107720</v>
@@ -15913,7 +15913,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>0.95082151889801</v>
+        <v>0.950821578502655</v>
       </c>
       <c r="H536" t="n">
         <v>11341148</v>
@@ -16029,7 +16029,7 @@
         <v>1.40950000286102</v>
       </c>
       <c r="G540" t="n">
-        <v>0.901266276836395</v>
+        <v>0.90126633644104</v>
       </c>
       <c r="H540" t="n">
         <v>12532316</v>
@@ -16087,7 +16087,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>0.898388981819153</v>
+        <v>0.898389041423798</v>
       </c>
       <c r="H542" t="n">
         <v>7219588</v>
@@ -16116,7 +16116,7 @@
         <v>1.43250000476837</v>
       </c>
       <c r="G543" t="n">
-        <v>0.915973007678986</v>
+        <v>0.915973126888275</v>
       </c>
       <c r="H543" t="n">
         <v>9600547</v>
@@ -16145,7 +16145,7 @@
         <v>1.41250002384186</v>
       </c>
       <c r="G544" t="n">
-        <v>0.903184711933136</v>
+        <v>0.903184652328491</v>
       </c>
       <c r="H544" t="n">
         <v>10997871</v>
@@ -16174,7 +16174,7 @@
         <v>1.42949998378754</v>
       </c>
       <c r="G545" t="n">
-        <v>0.914054811000824</v>
+        <v>0.914054870605469</v>
       </c>
       <c r="H545" t="n">
         <v>5848769</v>
@@ -16203,7 +16203,7 @@
         <v>1.41849994659424</v>
       </c>
       <c r="G546" t="n">
-        <v>0.907021105289459</v>
+        <v>0.907021224498749</v>
       </c>
       <c r="H546" t="n">
         <v>4186714</v>
@@ -16232,7 +16232,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G547" t="n">
-        <v>0.90222555398941</v>
+        <v>0.902225494384766</v>
       </c>
       <c r="H547" t="n">
         <v>5896451</v>
@@ -16319,7 +16319,7 @@
         <v>1.46899998188019</v>
       </c>
       <c r="G550" t="n">
-        <v>0.939311981201172</v>
+        <v>0.939311921596527</v>
       </c>
       <c r="H550" t="n">
         <v>13287558</v>
@@ -16348,7 +16348,7 @@
         <v>1.47950005531311</v>
       </c>
       <c r="G551" t="n">
-        <v>0.946025967597961</v>
+        <v>0.946025848388672</v>
       </c>
       <c r="H551" t="n">
         <v>11325965</v>
@@ -16406,7 +16406,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G553" t="n">
-        <v>0.930999398231506</v>
+        <v>0.930999517440796</v>
       </c>
       <c r="H553" t="n">
         <v>8244425</v>
@@ -16551,7 +16551,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>0.933557152748108</v>
+        <v>0.933557212352753</v>
       </c>
       <c r="H558" t="n">
         <v>8372703</v>
@@ -16580,7 +16580,7 @@
         <v>1.47950005531311</v>
       </c>
       <c r="G559" t="n">
-        <v>0.946025967597961</v>
+        <v>0.946025848388672</v>
       </c>
       <c r="H559" t="n">
         <v>9751449</v>
@@ -16609,7 +16609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G560" t="n">
-        <v>0.937393844127655</v>
+        <v>0.937393724918365</v>
       </c>
       <c r="H560" t="n">
         <v>8115149</v>
@@ -16667,7 +16667,7 @@
         <v>1.47950005531311</v>
       </c>
       <c r="G562" t="n">
-        <v>0.946025967597961</v>
+        <v>0.946025848388672</v>
       </c>
       <c r="H562" t="n">
         <v>8264270</v>
@@ -16696,7 +16696,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G563" t="n">
-        <v>0.939951479434967</v>
+        <v>0.939951539039612</v>
       </c>
       <c r="H563" t="n">
         <v>6842649</v>
@@ -16725,7 +16725,7 @@
         <v>1.48249995708466</v>
       </c>
       <c r="G564" t="n">
-        <v>0.947944104671478</v>
+        <v>0.947944283485413</v>
       </c>
       <c r="H564" t="n">
         <v>6234978</v>
@@ -16841,7 +16841,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G568" t="n">
-        <v>0.955936968326569</v>
+        <v>0.955937087535858</v>
       </c>
       <c r="H568" t="n">
         <v>18981853</v>
@@ -16870,7 +16870,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G569" t="n">
-        <v>0.94314843416214</v>
+        <v>0.943148553371429</v>
       </c>
       <c r="H569" t="n">
         <v>16092680</v>
@@ -16899,7 +16899,7 @@
         <v>1.50250005722046</v>
       </c>
       <c r="G570" t="n">
-        <v>0.960732638835907</v>
+        <v>0.960732877254486</v>
       </c>
       <c r="H570" t="n">
         <v>12817071</v>
@@ -16928,7 +16928,7 @@
         <v>1.49150002002716</v>
       </c>
       <c r="G571" t="n">
-        <v>0.953699052333832</v>
+        <v>0.953699171543121</v>
       </c>
       <c r="H571" t="n">
         <v>10859915</v>
@@ -16957,7 +16957,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G572" t="n">
-        <v>0.969364762306213</v>
+        <v>0.969364881515503</v>
       </c>
       <c r="H572" t="n">
         <v>9442871</v>
@@ -16986,7 +16986,7 @@
         <v>1.55250000953674</v>
       </c>
       <c r="G573" t="n">
-        <v>0.992703914642334</v>
+        <v>0.992703795433044</v>
       </c>
       <c r="H573" t="n">
         <v>13274432</v>
@@ -17073,7 +17073,7 @@
         <v>1.56649994850159</v>
       </c>
       <c r="G576" t="n">
-        <v>1.00165581703186</v>
+        <v>1.00165569782257</v>
       </c>
       <c r="H576" t="n">
         <v>12465064</v>
@@ -17131,7 +17131,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G578" t="n">
-        <v>1.01412463188171</v>
+        <v>1.01412451267242</v>
       </c>
       <c r="H578" t="n">
         <v>10827799</v>
@@ -17189,7 +17189,7 @@
         <v>1.57949995994568</v>
       </c>
       <c r="G580" t="n">
-        <v>1.00996828079224</v>
+        <v>1.00996816158295</v>
       </c>
       <c r="H580" t="n">
         <v>12622480</v>
@@ -17305,7 +17305,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G584" t="n">
-        <v>1.02499449253082</v>
+        <v>1.0249947309494</v>
       </c>
       <c r="H584" t="n">
         <v>7584397</v>
@@ -17334,7 +17334,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G585" t="n">
-        <v>1.03266787528992</v>
+        <v>1.03266775608063</v>
       </c>
       <c r="H585" t="n">
         <v>10428043</v>
@@ -17450,7 +17450,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G589" t="n">
-        <v>1.04481685161591</v>
+        <v>1.04481673240662</v>
       </c>
       <c r="H589" t="n">
         <v>6633206</v>
@@ -17537,7 +17537,7 @@
         <v>1.67449998855591</v>
       </c>
       <c r="G592" t="n">
-        <v>1.07071328163147</v>
+        <v>1.07071340084076</v>
       </c>
       <c r="H592" t="n">
         <v>13321309</v>
@@ -17653,7 +17653,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G596" t="n">
-        <v>1.0569657087326</v>
+        <v>1.05696582794189</v>
       </c>
       <c r="H596" t="n">
         <v>12540038</v>
@@ -17682,7 +17682,7 @@
         <v>1.67550003528595</v>
       </c>
       <c r="G597" t="n">
-        <v>1.07135272026062</v>
+        <v>1.07135283946991</v>
       </c>
       <c r="H597" t="n">
         <v>11881396</v>
@@ -17711,7 +17711,7 @@
         <v>1.68649995326996</v>
       </c>
       <c r="G598" t="n">
-        <v>1.07838642597198</v>
+        <v>1.0783863067627</v>
       </c>
       <c r="H598" t="n">
         <v>7405425</v>
@@ -17885,7 +17885,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G604" t="n">
-        <v>1.03650450706482</v>
+        <v>1.03650438785553</v>
       </c>
       <c r="H604" t="n">
         <v>9445524</v>
@@ -17914,7 +17914,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G605" t="n">
-        <v>1.00517272949219</v>
+        <v>1.0051726102829</v>
       </c>
       <c r="H605" t="n">
         <v>17531249</v>
@@ -17943,7 +17943,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G606" t="n">
-        <v>1.0090092420578</v>
+        <v>1.00900912284851</v>
       </c>
       <c r="H606" t="n">
         <v>9195189</v>
@@ -17972,7 +17972,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G607" t="n">
-        <v>0.986629247665405</v>
+        <v>0.986629366874695</v>
       </c>
       <c r="H607" t="n">
         <v>13358750</v>
@@ -18001,7 +18001,7 @@
         <v>1.49249994754791</v>
       </c>
       <c r="G608" t="n">
-        <v>0.991478800773621</v>
+        <v>0.991478681564331</v>
       </c>
       <c r="H608" t="n">
         <v>19030256</v>
@@ -18030,7 +18030,7 @@
         <v>1.51250004768372</v>
       </c>
       <c r="G609" t="n">
-        <v>1.00476503372192</v>
+        <v>1.00476491451263</v>
       </c>
       <c r="H609" t="n">
         <v>12422911</v>
@@ -18059,7 +18059,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G610" t="n">
-        <v>0.994468152523041</v>
+        <v>0.99446827173233</v>
       </c>
       <c r="H610" t="n">
         <v>11157722</v>
@@ -18088,7 +18088,7 @@
         <v>1.50450003147125</v>
       </c>
       <c r="G611" t="n">
-        <v>0.999450385570526</v>
+        <v>0.999450445175171</v>
       </c>
       <c r="H611" t="n">
         <v>16007406</v>
@@ -18204,7 +18204,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>0.953281044960022</v>
+        <v>0.953281104564667</v>
       </c>
       <c r="H615" t="n">
         <v>14605759</v>
@@ -18233,7 +18233,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G616" t="n">
-        <v>0.964574337005615</v>
+        <v>0.964574456214905</v>
       </c>
       <c r="H616" t="n">
         <v>19464065</v>
@@ -18349,7 +18349,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G620" t="n">
-        <v>0.960588455200195</v>
+        <v>0.960588574409485</v>
       </c>
       <c r="H620" t="n">
         <v>9315091</v>
@@ -18378,7 +18378,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G621" t="n">
-        <v>0.953945219516754</v>
+        <v>0.953945338726044</v>
       </c>
       <c r="H621" t="n">
         <v>8534388</v>
@@ -18407,7 +18407,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G622" t="n">
-        <v>0.92471581697464</v>
+        <v>0.924715876579285</v>
       </c>
       <c r="H622" t="n">
         <v>7934522</v>
@@ -18436,7 +18436,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G623" t="n">
-        <v>0.953945219516754</v>
+        <v>0.953945338726044</v>
       </c>
       <c r="H623" t="n">
         <v>7636200</v>
@@ -18465,7 +18465,7 @@
         <v>1.45949995517731</v>
       </c>
       <c r="G624" t="n">
-        <v>0.969556510448456</v>
+        <v>0.969556629657745</v>
       </c>
       <c r="H624" t="n">
         <v>20453135</v>
@@ -18494,7 +18494,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G625" t="n">
-        <v>0.977196097373962</v>
+        <v>0.977196216583252</v>
       </c>
       <c r="H625" t="n">
         <v>7638784</v>
@@ -18523,7 +18523,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G626" t="n">
-        <v>0.984503507614136</v>
+        <v>0.984503388404846</v>
       </c>
       <c r="H626" t="n">
         <v>10928121</v>
@@ -18552,7 +18552,7 @@
         <v>1.47749996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>0.981514155864716</v>
+        <v>0.981514036655426</v>
       </c>
       <c r="H627" t="n">
         <v>11015985</v>
@@ -18610,7 +18610,7 @@
         <v>1.49950003623962</v>
       </c>
       <c r="G629" t="n">
-        <v>0.996129035949707</v>
+        <v>0.996128916740417</v>
       </c>
       <c r="H629" t="n">
         <v>14038839</v>
@@ -18697,7 +18697,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G632" t="n">
-        <v>0.97852486371994</v>
+        <v>0.978524744510651</v>
       </c>
       <c r="H632" t="n">
         <v>7978518</v>
@@ -18755,7 +18755,7 @@
         <v>1.45449995994568</v>
       </c>
       <c r="G634" t="n">
-        <v>0.966235220432281</v>
+        <v>0.966235101222992</v>
       </c>
       <c r="H634" t="n">
         <v>8111462</v>
@@ -18813,7 +18813,7 @@
         <v>1.47449994087219</v>
       </c>
       <c r="G636" t="n">
-        <v>0.979521155357361</v>
+        <v>0.97952127456665</v>
       </c>
       <c r="H636" t="n">
         <v>7436615</v>
@@ -18871,7 +18871,7 @@
         <v>1.45650005340576</v>
       </c>
       <c r="G638" t="n">
-        <v>0.96756374835968</v>
+        <v>0.967563629150391</v>
       </c>
       <c r="H638" t="n">
         <v>5968968</v>
@@ -18900,7 +18900,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G639" t="n">
-        <v>0.991146624088287</v>
+        <v>0.991146504878998</v>
       </c>
       <c r="H639" t="n">
         <v>7895696</v>
@@ -19016,7 +19016,7 @@
         <v>1.52300000190735</v>
       </c>
       <c r="G643" t="n">
-        <v>1.01173996925354</v>
+        <v>1.01174032688141</v>
       </c>
       <c r="H643" t="n">
         <v>4012228</v>
@@ -19045,7 +19045,7 @@
         <v>1.52649998664856</v>
       </c>
       <c r="G644" t="n">
-        <v>1.01406538486481</v>
+        <v>1.01406526565552</v>
       </c>
       <c r="H644" t="n">
         <v>4908311</v>
@@ -19132,7 +19132,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G647" t="n">
-        <v>1.01838314533234</v>
+        <v>1.01838326454163</v>
       </c>
       <c r="H647" t="n">
         <v>4628689</v>
@@ -19190,7 +19190,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G649" t="n">
-        <v>1.04296255111694</v>
+        <v>1.04296243190765</v>
       </c>
       <c r="H649" t="n">
         <v>7014996</v>
@@ -19277,7 +19277,7 @@
         <v>1.55750000476837</v>
       </c>
       <c r="G652" t="n">
-        <v>1.03465867042542</v>
+        <v>1.0346587896347</v>
       </c>
       <c r="H652" t="n">
         <v>9471447</v>
@@ -19364,7 +19364,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G655" t="n">
-        <v>1.01306879520416</v>
+        <v>1.01306867599487</v>
       </c>
       <c r="H655" t="n">
         <v>11456358</v>
@@ -19393,7 +19393,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>1.02303326129913</v>
+        <v>1.02303338050842</v>
       </c>
       <c r="H656" t="n">
         <v>6977301</v>
@@ -19422,7 +19422,7 @@
         <v>1.54550004005432</v>
       </c>
       <c r="G657" t="n">
-        <v>1.02668714523315</v>
+        <v>1.02668690681458</v>
       </c>
       <c r="H657" t="n">
         <v>5880662</v>
@@ -19480,7 +19480,7 @@
         <v>1.57149994373322</v>
       </c>
       <c r="G659" t="n">
-        <v>1.04395890235901</v>
+        <v>1.0439590215683</v>
       </c>
       <c r="H659" t="n">
         <v>21334091</v>
@@ -19509,7 +19509,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G660" t="n">
-        <v>1.03166937828064</v>
+        <v>1.03166925907135</v>
       </c>
       <c r="H660" t="n">
         <v>18333054</v>
@@ -19538,7 +19538,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>1.02303326129913</v>
+        <v>1.02303338050842</v>
       </c>
       <c r="H661" t="n">
         <v>13634160</v>
@@ -19567,7 +19567,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G662" t="n">
-        <v>1.04030525684357</v>
+        <v>1.04030549526215</v>
       </c>
       <c r="H662" t="n">
         <v>8852451</v>
@@ -19654,7 +19654,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G665" t="n">
-        <v>1.06887066364288</v>
+        <v>1.06887054443359</v>
       </c>
       <c r="H665" t="n">
         <v>15024786</v>
@@ -19683,7 +19683,7 @@
         <v>1.61450004577637</v>
       </c>
       <c r="G666" t="n">
-        <v>1.07252418994904</v>
+        <v>1.07252430915833</v>
       </c>
       <c r="H666" t="n">
         <v>8629808</v>
@@ -19741,7 +19741,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>1.05558431148529</v>
+        <v>1.05558443069458</v>
       </c>
       <c r="H668" t="n">
         <v>7470929</v>
@@ -19828,7 +19828,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G671" t="n">
-        <v>1.05890595912933</v>
+        <v>1.05890583992004</v>
       </c>
       <c r="H671" t="n">
         <v>8931453</v>
@@ -19886,7 +19886,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G673" t="n">
-        <v>1.03831231594086</v>
+        <v>1.03831243515015</v>
       </c>
       <c r="H673" t="n">
         <v>10463219</v>
@@ -19915,7 +19915,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.03964114189148</v>
+        <v>1.03964102268219</v>
       </c>
       <c r="H674" t="n">
         <v>8082626</v>
@@ -19944,7 +19944,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G675" t="n">
-        <v>1.04030525684357</v>
+        <v>1.04030549526215</v>
       </c>
       <c r="H675" t="n">
         <v>6844426</v>
@@ -20060,7 +20060,7 @@
         <v>1.49749994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>0.994800269603729</v>
+        <v>0.99480015039444</v>
       </c>
       <c r="H679" t="n">
         <v>7575712</v>
@@ -20089,7 +20089,7 @@
         <v>1.46749997138977</v>
       </c>
       <c r="G680" t="n">
-        <v>0.974871098995209</v>
+        <v>0.974870979785919</v>
       </c>
       <c r="H680" t="n">
         <v>6477331</v>
@@ -20118,7 +20118,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G681" t="n">
-        <v>0.983839154243469</v>
+        <v>0.98383903503418</v>
       </c>
       <c r="H681" t="n">
         <v>7923572</v>
@@ -20292,7 +20292,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.02967631816864</v>
+        <v>1.02967643737793</v>
       </c>
       <c r="H687" t="n">
         <v>10750488</v>
@@ -20379,7 +20379,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G690" t="n">
-        <v>1.0349907875061</v>
+        <v>1.03499090671539</v>
       </c>
       <c r="H690" t="n">
         <v>7238747</v>
@@ -20408,7 +20408,7 @@
         <v>1.55350005626678</v>
       </c>
       <c r="G691" t="n">
-        <v>1.03200137615204</v>
+        <v>1.03200149536133</v>
       </c>
       <c r="H691" t="n">
         <v>4294867</v>
@@ -20437,7 +20437,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G692" t="n">
-        <v>1.04827702045441</v>
+        <v>1.0482771396637</v>
       </c>
       <c r="H692" t="n">
         <v>9265488</v>
@@ -20495,7 +20495,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G694" t="n">
-        <v>1.03166937828064</v>
+        <v>1.03166925907135</v>
       </c>
       <c r="H694" t="n">
         <v>6733660</v>
@@ -20524,7 +20524,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G695" t="n">
-        <v>1.02701914310455</v>
+        <v>1.02701926231384</v>
       </c>
       <c r="H695" t="n">
         <v>10240668</v>
@@ -20611,7 +20611,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G698" t="n">
-        <v>1.02701914310455</v>
+        <v>1.02701926231384</v>
       </c>
       <c r="H698" t="n">
         <v>7919098</v>
@@ -20669,7 +20669,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>1.02037620544434</v>
+        <v>1.02037596702576</v>
       </c>
       <c r="H700" t="n">
         <v>5527999</v>
@@ -20698,7 +20698,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G701" t="n">
-        <v>0.993139505386353</v>
+        <v>0.993139624595642</v>
       </c>
       <c r="H701" t="n">
         <v>10053107</v>
@@ -20727,7 +20727,7 @@
         <v>1.48249995708466</v>
       </c>
       <c r="G702" t="n">
-        <v>0.984835624694824</v>
+        <v>0.984835743904114</v>
       </c>
       <c r="H702" t="n">
         <v>7479148</v>
@@ -20756,7 +20756,7 @@
         <v>1.50049996376038</v>
       </c>
       <c r="G703" t="n">
-        <v>0.996793150901794</v>
+        <v>0.996793270111084</v>
       </c>
       <c r="H703" t="n">
         <v>7222392</v>
@@ -20785,7 +20785,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>1.02303326129913</v>
+        <v>1.02303338050842</v>
       </c>
       <c r="H704" t="n">
         <v>7080938</v>
@@ -20843,7 +20843,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G706" t="n">
-        <v>1.00376844406128</v>
+        <v>1.00376832485199</v>
       </c>
       <c r="H706" t="n">
         <v>8299178</v>
@@ -20901,7 +20901,7 @@
         <v>1.52049994468689</v>
       </c>
       <c r="G708" t="n">
-        <v>1.01007950305939</v>
+        <v>1.01007926464081</v>
       </c>
       <c r="H708" t="n">
         <v>6622882</v>
@@ -20930,7 +20930,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G709" t="n">
-        <v>0.987160742282867</v>
+        <v>0.987160861492157</v>
       </c>
       <c r="H709" t="n">
         <v>7876441</v>
@@ -20988,7 +20988,7 @@
         <v>1.42449998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>0.946305811405182</v>
+        <v>0.946305871009827</v>
       </c>
       <c r="H711" t="n">
         <v>7082723</v>
@@ -21017,7 +21017,7 @@
         <v>1.4485000371933</v>
       </c>
       <c r="G712" t="n">
-        <v>0.962249219417572</v>
+        <v>0.962249338626862</v>
       </c>
       <c r="H712" t="n">
         <v>6393512</v>
@@ -21162,7 +21162,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G717" t="n">
-        <v>0.971217453479767</v>
+        <v>0.971217334270477</v>
       </c>
       <c r="H717" t="n">
         <v>9054359</v>
@@ -21220,7 +21220,7 @@
         <v>1.42750000953674</v>
       </c>
       <c r="G719" t="n">
-        <v>0.948298752307892</v>
+        <v>0.948298871517181</v>
       </c>
       <c r="H719" t="n">
         <v>7837348</v>
@@ -21249,7 +21249,7 @@
         <v>1.41949999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>0.942984282970428</v>
+        <v>0.942984342575073</v>
       </c>
       <c r="H720" t="n">
         <v>15134461</v>
@@ -21278,7 +21278,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G721" t="n">
-        <v>0.932687640190125</v>
+        <v>0.932687401771545</v>
       </c>
       <c r="H721" t="n">
         <v>5292426</v>
@@ -21307,7 +21307,7 @@
         <v>1.44449996948242</v>
       </c>
       <c r="G722" t="n">
-        <v>0.959591865539551</v>
+        <v>0.95959198474884</v>
       </c>
       <c r="H722" t="n">
         <v>9978343</v>
@@ -21365,7 +21365,7 @@
         <v>1.42449998855591</v>
       </c>
       <c r="G724" t="n">
-        <v>0.946305811405182</v>
+        <v>0.946305871009827</v>
       </c>
       <c r="H724" t="n">
         <v>8955250</v>
@@ -21423,7 +21423,7 @@
         <v>1.42550003528595</v>
       </c>
       <c r="G726" t="n">
-        <v>0.946970283985138</v>
+        <v>0.946970224380493</v>
       </c>
       <c r="H726" t="n">
         <v>9148384</v>
@@ -21452,7 +21452,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G727" t="n">
-        <v>0.938001990318298</v>
+        <v>0.938001930713654</v>
       </c>
       <c r="H727" t="n">
         <v>7441327</v>
@@ -21481,7 +21481,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>0.946637809276581</v>
+        <v>0.946637988090515</v>
       </c>
       <c r="H728" t="n">
         <v>11126130</v>
@@ -21510,7 +21510,7 @@
         <v>1.45550000667572</v>
       </c>
       <c r="G729" t="n">
-        <v>0.966899335384369</v>
+        <v>0.966899454593658</v>
       </c>
       <c r="H729" t="n">
         <v>7078981</v>
@@ -21568,7 +21568,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G731" t="n">
-        <v>0.973874628543854</v>
+        <v>0.973874509334564</v>
       </c>
       <c r="H731" t="n">
         <v>13355634</v>
@@ -21626,7 +21626,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G733" t="n">
-        <v>0.9878249168396</v>
+        <v>0.987825036048889</v>
       </c>
       <c r="H733" t="n">
         <v>14445058</v>
@@ -21655,7 +21655,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G734" t="n">
-        <v>0.993139505386353</v>
+        <v>0.993139624595642</v>
       </c>
       <c r="H734" t="n">
         <v>9727607</v>
@@ -21684,7 +21684,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G735" t="n">
-        <v>0.991810917854309</v>
+        <v>0.99181079864502</v>
       </c>
       <c r="H735" t="n">
         <v>10486420</v>
@@ -21713,7 +21713,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G736" t="n">
-        <v>1.00376844406128</v>
+        <v>1.00376832485199</v>
       </c>
       <c r="H736" t="n">
         <v>7985862</v>
@@ -21742,7 +21742,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G737" t="n">
-        <v>1.00443267822266</v>
+        <v>1.00443279743195</v>
       </c>
       <c r="H737" t="n">
         <v>7763032</v>
@@ -21771,7 +21771,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G738" t="n">
-        <v>1.00642573833466</v>
+        <v>1.00642561912537</v>
       </c>
       <c r="H738" t="n">
         <v>10500643</v>
@@ -21829,7 +21829,7 @@
         <v>1.47549998760223</v>
       </c>
       <c r="G740" t="n">
-        <v>0.980185508728027</v>
+        <v>0.980185389518738</v>
       </c>
       <c r="H740" t="n">
         <v>6484898</v>
@@ -21858,7 +21858,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G741" t="n">
-        <v>0.992475032806396</v>
+        <v>0.992475152015686</v>
       </c>
       <c r="H741" t="n">
         <v>4431597</v>
@@ -21887,7 +21887,7 @@
         <v>1.53149998188019</v>
       </c>
       <c r="G742" t="n">
-        <v>1.01738667488098</v>
+        <v>1.01738679409027</v>
       </c>
       <c r="H742" t="n">
         <v>8733035</v>
@@ -21945,7 +21945,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G744" t="n">
-        <v>0.983839154243469</v>
+        <v>0.98383903503418</v>
       </c>
       <c r="H744" t="n">
         <v>9442553</v>
@@ -22003,7 +22003,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G746" t="n">
-        <v>0.987160742282867</v>
+        <v>0.987160861492157</v>
       </c>
       <c r="H746" t="n">
         <v>6273234</v>
@@ -22032,7 +22032,7 @@
         <v>1.50450003147125</v>
       </c>
       <c r="G747" t="n">
-        <v>0.999450385570526</v>
+        <v>0.999450445175171</v>
       </c>
       <c r="H747" t="n">
         <v>5070699</v>
@@ -22061,7 +22061,7 @@
         <v>1.494500041008</v>
       </c>
       <c r="G748" t="n">
-        <v>0.992807388305664</v>
+        <v>0.992807507514954</v>
       </c>
       <c r="H748" t="n">
         <v>7203899</v>
@@ -22090,7 +22090,7 @@
         <v>1.50049996376038</v>
       </c>
       <c r="G749" t="n">
-        <v>0.996793150901794</v>
+        <v>0.996793270111084</v>
       </c>
       <c r="H749" t="n">
         <v>5582112</v>
@@ -22206,7 +22206,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G753" t="n">
-        <v>1.02502620220184</v>
+        <v>1.02502632141113</v>
       </c>
       <c r="H753" t="n">
         <v>11282988</v>
@@ -22235,7 +22235,7 @@
         <v>1.58150005340576</v>
       </c>
       <c r="G754" t="n">
-        <v>1.05060207843781</v>
+        <v>1.05060219764709</v>
       </c>
       <c r="H754" t="n">
         <v>12075235</v>
@@ -22264,7 +22264,7 @@
         <v>1.60549998283386</v>
       </c>
       <c r="G755" t="n">
-        <v>1.0665454864502</v>
+        <v>1.06654536724091</v>
       </c>
       <c r="H755" t="n">
         <v>12142941</v>
@@ -22293,7 +22293,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G756" t="n">
-        <v>1.07551348209381</v>
+        <v>1.0755136013031</v>
       </c>
       <c r="H756" t="n">
         <v>11186605</v>
@@ -22322,7 +22322,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G757" t="n">
-        <v>1.06289172172546</v>
+        <v>1.06289160251617</v>
       </c>
       <c r="H757" t="n">
         <v>11826480</v>
@@ -22380,7 +22380,7 @@
         <v>1.61349999904633</v>
       </c>
       <c r="G759" t="n">
-        <v>1.07186007499695</v>
+        <v>1.07185995578766</v>
       </c>
       <c r="H759" t="n">
         <v>9122531</v>
@@ -22409,7 +22409,7 @@
         <v>1.625</v>
       </c>
       <c r="G760" t="n">
-        <v>1.07949948310852</v>
+        <v>1.07949936389923</v>
       </c>
       <c r="H760" t="n">
         <v>7824444</v>
@@ -22438,7 +22438,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G761" t="n">
-        <v>1.06355595588684</v>
+        <v>1.06355607509613</v>
       </c>
       <c r="H761" t="n">
         <v>10273563</v>
@@ -22467,7 +22467,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G762" t="n">
-        <v>1.03897678852081</v>
+        <v>1.03897655010223</v>
       </c>
       <c r="H762" t="n">
         <v>5540437</v>
@@ -22496,7 +22496,7 @@
         <v>1.57249999046326</v>
       </c>
       <c r="G763" t="n">
-        <v>1.04462325572968</v>
+        <v>1.04462337493896</v>
       </c>
       <c r="H763" t="n">
         <v>3949707</v>
@@ -22554,7 +22554,7 @@
         <v>1.6065000295639</v>
       </c>
       <c r="G765" t="n">
-        <v>1.06720972061157</v>
+        <v>1.06720983982086</v>
       </c>
       <c r="H765" t="n">
         <v>8526842</v>
@@ -22612,7 +22612,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G767" t="n">
-        <v>1.08481407165527</v>
+        <v>1.08481395244598</v>
       </c>
       <c r="H767" t="n">
         <v>10307735</v>
@@ -22699,7 +22699,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G770" t="n">
-        <v>1.05359148979187</v>
+        <v>1.05359160900116</v>
       </c>
       <c r="H770" t="n">
         <v>23589368</v>
@@ -22902,7 +22902,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G777" t="n">
-        <v>1.04827702045441</v>
+        <v>1.0482771396637</v>
       </c>
       <c r="H777" t="n">
         <v>4051995</v>
@@ -22931,7 +22931,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G778" t="n">
-        <v>1.04296255111694</v>
+        <v>1.04296243190765</v>
       </c>
       <c r="H778" t="n">
         <v>2899119</v>
@@ -22989,7 +22989,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G780" t="n">
-        <v>1.03897678852081</v>
+        <v>1.03897655010223</v>
       </c>
       <c r="H780" t="n">
         <v>6894573</v>
@@ -23018,7 +23018,7 @@
         <v>1.54849994182587</v>
       </c>
       <c r="G781" t="n">
-        <v>1.02867984771729</v>
+        <v>1.02867996692657</v>
       </c>
       <c r="H781" t="n">
         <v>11703834</v>
@@ -23047,7 +23047,7 @@
         <v>1.55750000476837</v>
       </c>
       <c r="G782" t="n">
-        <v>1.03465867042542</v>
+        <v>1.0346587896347</v>
       </c>
       <c r="H782" t="n">
         <v>7860675</v>
@@ -23192,7 +23192,7 @@
         <v>1.55350005626678</v>
       </c>
       <c r="G787" t="n">
-        <v>1.03200137615204</v>
+        <v>1.03200149536133</v>
       </c>
       <c r="H787" t="n">
         <v>6492402</v>
@@ -23221,7 +23221,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G788" t="n">
-        <v>1.03964114189148</v>
+        <v>1.03964102268219</v>
       </c>
       <c r="H788" t="n">
         <v>7656593</v>
@@ -23250,7 +23250,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G789" t="n">
-        <v>1.03698372840881</v>
+        <v>1.0369838476181</v>
       </c>
       <c r="H789" t="n">
         <v>4962271</v>
@@ -23279,7 +23279,7 @@
         <v>1.54550004005432</v>
       </c>
       <c r="G790" t="n">
-        <v>1.02668714523315</v>
+        <v>1.02668690681458</v>
       </c>
       <c r="H790" t="n">
         <v>8730632</v>
@@ -23308,7 +23308,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G791" t="n">
-        <v>1.01373314857483</v>
+        <v>1.01373302936554</v>
       </c>
       <c r="H791" t="n">
         <v>8026636</v>
@@ -23366,7 +23366,7 @@
         <v>1.55550003051758</v>
       </c>
       <c r="G793" t="n">
-        <v>1.03333032131195</v>
+        <v>1.03333020210266</v>
       </c>
       <c r="H793" t="n">
         <v>5147849</v>
@@ -23395,7 +23395,7 @@
         <v>1.57149994373322</v>
       </c>
       <c r="G794" t="n">
-        <v>1.04395890235901</v>
+        <v>1.0439590215683</v>
       </c>
       <c r="H794" t="n">
         <v>6425027</v>
@@ -23453,7 +23453,7 @@
         <v>1.58050000667572</v>
       </c>
       <c r="G796" t="n">
-        <v>1.04993784427643</v>
+        <v>1.04993796348572</v>
       </c>
       <c r="H796" t="n">
         <v>7608597</v>
@@ -23511,7 +23511,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G798" t="n">
-        <v>1.04761266708374</v>
+        <v>1.04761278629303</v>
       </c>
       <c r="H798" t="n">
         <v>4298694</v>
@@ -23598,7 +23598,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G801" t="n">
-        <v>1.05359148979187</v>
+        <v>1.05359160900116</v>
       </c>
       <c r="H801" t="n">
         <v>7476429</v>
@@ -23656,7 +23656,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G803" t="n">
-        <v>1.04761266708374</v>
+        <v>1.04761278629303</v>
       </c>
       <c r="H803" t="n">
         <v>8877266</v>
@@ -23714,7 +23714,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G805" t="n">
-        <v>1.0349907875061</v>
+        <v>1.03499090671539</v>
       </c>
       <c r="H805" t="n">
         <v>7593428</v>
@@ -23801,7 +23801,7 @@
         <v>1.56449997425079</v>
       </c>
       <c r="G808" t="n">
-        <v>1.0393089056015</v>
+        <v>1.03930878639221</v>
       </c>
       <c r="H808" t="n">
         <v>6122184</v>
@@ -23830,7 +23830,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G809" t="n">
-        <v>1.04296255111694</v>
+        <v>1.04296243190765</v>
       </c>
       <c r="H809" t="n">
         <v>8250933</v>
@@ -23888,7 +23888,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G811" t="n">
-        <v>1.06887066364288</v>
+        <v>1.06887054443359</v>
       </c>
       <c r="H811" t="n">
         <v>6002078</v>
@@ -23946,7 +23946,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G813" t="n">
-        <v>1.06289172172546</v>
+        <v>1.06289160251617</v>
       </c>
       <c r="H813" t="n">
         <v>5577878</v>
@@ -23975,7 +23975,7 @@
         <v>1.60549998283386</v>
       </c>
       <c r="G814" t="n">
-        <v>1.0665454864502</v>
+        <v>1.06654536724091</v>
       </c>
       <c r="H814" t="n">
         <v>5417785</v>
@@ -24033,7 +24033,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G816" t="n">
-        <v>1.05691301822662</v>
+        <v>1.05691289901733</v>
       </c>
       <c r="H816" t="n">
         <v>9665784</v>
@@ -24062,7 +24062,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G817" t="n">
-        <v>1.05957019329071</v>
+        <v>1.0595703125</v>
       </c>
       <c r="H817" t="n">
         <v>4413361</v>
@@ -24091,7 +24091,7 @@
         <v>1.60549998283386</v>
       </c>
       <c r="G818" t="n">
-        <v>1.0665454864502</v>
+        <v>1.06654536724091</v>
       </c>
       <c r="H818" t="n">
         <v>4741166</v>
@@ -24207,7 +24207,7 @@
         <v>1.61349999904633</v>
       </c>
       <c r="G822" t="n">
-        <v>1.07186007499695</v>
+        <v>1.07185995578766</v>
       </c>
       <c r="H822" t="n">
         <v>6400119</v>
@@ -24236,7 +24236,7 @@
         <v>1.63150000572205</v>
       </c>
       <c r="G823" t="n">
-        <v>1.08381748199463</v>
+        <v>1.08381736278534</v>
       </c>
       <c r="H823" t="n">
         <v>6878368</v>
@@ -24265,7 +24265,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G824" t="n">
-        <v>1.08348524570465</v>
+        <v>1.08348536491394</v>
       </c>
       <c r="H824" t="n">
         <v>9421547</v>
@@ -24294,7 +24294,7 @@
         <v>1.62450003623962</v>
       </c>
       <c r="G825" t="n">
-        <v>1.07916748523712</v>
+        <v>1.07916736602783</v>
       </c>
       <c r="H825" t="n">
         <v>6723386</v>
@@ -24352,7 +24352,7 @@
         <v>1.62450003623962</v>
       </c>
       <c r="G827" t="n">
-        <v>1.07916748523712</v>
+        <v>1.07916736602783</v>
       </c>
       <c r="H827" t="n">
         <v>7204900</v>
@@ -24410,7 +24410,7 @@
         <v>1.60549998283386</v>
       </c>
       <c r="G829" t="n">
-        <v>1.0665454864502</v>
+        <v>1.06654536724091</v>
       </c>
       <c r="H829" t="n">
         <v>23080149</v>
@@ -24439,7 +24439,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G830" t="n">
-        <v>1.04296255111694</v>
+        <v>1.04296243190765</v>
       </c>
       <c r="H830" t="n">
         <v>23194933</v>
@@ -24468,7 +24468,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G831" t="n">
-        <v>1.02502620220184</v>
+        <v>1.02502632141113</v>
       </c>
       <c r="H831" t="n">
         <v>18831227</v>
@@ -24497,7 +24497,7 @@
         <v>1.5275000333786</v>
       </c>
       <c r="G832" t="n">
-        <v>1.0147293806076</v>
+        <v>1.01472949981689</v>
       </c>
       <c r="H832" t="n">
         <v>13297215</v>
@@ -24526,7 +24526,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G833" t="n">
-        <v>1.00443267822266</v>
+        <v>1.00443279743195</v>
       </c>
       <c r="H833" t="n">
         <v>20235158</v>
@@ -24613,7 +24613,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G836" t="n">
-        <v>0.992475032806396</v>
+        <v>0.992475152015686</v>
       </c>
       <c r="H836" t="n">
         <v>15240423</v>
@@ -24642,7 +24642,7 @@
         <v>1.51450002193451</v>
       </c>
       <c r="G837" t="n">
-        <v>1.00609350204468</v>
+        <v>1.00609362125397</v>
       </c>
       <c r="H837" t="n">
         <v>17753645</v>
@@ -24700,7 +24700,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G839" t="n">
-        <v>0.984503507614136</v>
+        <v>0.984503388404846</v>
       </c>
       <c r="H839" t="n">
         <v>14879230</v>
@@ -24816,7 +24816,7 @@
         <v>1.47749996185303</v>
       </c>
       <c r="G843" t="n">
-        <v>0.981514155864716</v>
+        <v>0.981514036655426</v>
       </c>
       <c r="H843" t="n">
         <v>5819774</v>
@@ -24874,7 +24874,7 @@
         <v>1.47150003910065</v>
       </c>
       <c r="G845" t="n">
-        <v>0.977528274059296</v>
+        <v>0.977528393268585</v>
       </c>
       <c r="H845" t="n">
         <v>8663663</v>
@@ -24932,7 +24932,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G847" t="n">
-        <v>0.973874628543854</v>
+        <v>0.973874509334564</v>
       </c>
       <c r="H847" t="n">
         <v>12506781</v>
@@ -24961,7 +24961,7 @@
         <v>1.46449995040894</v>
       </c>
       <c r="G848" t="n">
-        <v>0.972878098487854</v>
+        <v>0.972877979278564</v>
       </c>
       <c r="H848" t="n">
         <v>11257238</v>
@@ -24990,7 +24990,7 @@
         <v>1.45949995517731</v>
       </c>
       <c r="G849" t="n">
-        <v>0.969556510448456</v>
+        <v>0.969556629657745</v>
       </c>
       <c r="H849" t="n">
         <v>12564250</v>
@@ -25019,7 +25019,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>0.969888627529144</v>
+        <v>0.969888865947723</v>
       </c>
       <c r="H850" t="n">
         <v>13778936</v>
@@ -25077,7 +25077,7 @@
         <v>1.43350005149841</v>
       </c>
       <c r="G852" t="n">
-        <v>0.952284693717957</v>
+        <v>0.952284634113312</v>
       </c>
       <c r="H852" t="n">
         <v>10761663</v>
@@ -25106,7 +25106,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G853" t="n">
-        <v>0.961252868175507</v>
+        <v>0.961252808570862</v>
       </c>
       <c r="H853" t="n">
         <v>9112473</v>
@@ -25164,7 +25164,7 @@
         <v>1.46749997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>0.974871098995209</v>
+        <v>0.974870979785919</v>
       </c>
       <c r="H855" t="n">
         <v>9852378</v>
@@ -25222,7 +25222,7 @@
         <v>1.54649996757507</v>
       </c>
       <c r="G857" t="n">
-        <v>1.02735114097595</v>
+        <v>1.02735126018524</v>
       </c>
       <c r="H857" t="n">
         <v>26160095</v>
@@ -25251,7 +25251,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>1.02967631816864</v>
+        <v>1.02967643737793</v>
       </c>
       <c r="H858" t="n">
         <v>18068522</v>
@@ -25280,7 +25280,7 @@
         <v>1.48849999904633</v>
       </c>
       <c r="G859" t="n">
-        <v>1.03559005260468</v>
+        <v>1.03559017181396</v>
       </c>
       <c r="H859" t="n">
         <v>12966238</v>
@@ -25338,7 +25338,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G861" t="n">
-        <v>1.04637384414673</v>
+        <v>1.04637396335602</v>
       </c>
       <c r="H861" t="n">
         <v>10507190</v>
@@ -25367,7 +25367,7 @@
         <v>1.46249997615814</v>
       </c>
       <c r="G862" t="n">
-        <v>1.01750123500824</v>
+        <v>1.01750135421753</v>
       </c>
       <c r="H862" t="n">
         <v>11985933</v>
@@ -25396,7 +25396,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G863" t="n">
-        <v>1.04637384414673</v>
+        <v>1.04637396335602</v>
       </c>
       <c r="H863" t="n">
         <v>11577558</v>
@@ -25454,7 +25454,7 @@
         <v>1.47049999237061</v>
       </c>
       <c r="G865" t="n">
-        <v>1.02306687831879</v>
+        <v>1.02306699752808</v>
       </c>
       <c r="H865" t="n">
         <v>7257271</v>
@@ -25512,7 +25512,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G867" t="n">
-        <v>1.00323879718781</v>
+        <v>1.00323891639709</v>
       </c>
       <c r="H867" t="n">
         <v>5300830</v>
@@ -25541,7 +25541,7 @@
         <v>1.45949995517731</v>
       </c>
       <c r="G868" t="n">
-        <v>1.0154139995575</v>
+        <v>1.01541388034821</v>
       </c>
       <c r="H868" t="n">
         <v>13634011</v>
@@ -25570,7 +25570,7 @@
         <v>1.47049999237061</v>
       </c>
       <c r="G869" t="n">
-        <v>1.02306687831879</v>
+        <v>1.02306699752808</v>
       </c>
       <c r="H869" t="n">
         <v>7586484</v>
@@ -25657,7 +25657,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G872" t="n">
-        <v>1.04637384414673</v>
+        <v>1.04637396335602</v>
       </c>
       <c r="H872" t="n">
         <v>10787760</v>
@@ -25686,7 +25686,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G873" t="n">
-        <v>1.04776537418365</v>
+        <v>1.04776525497437</v>
       </c>
       <c r="H873" t="n">
         <v>9293008</v>
@@ -25744,7 +25744,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G875" t="n">
-        <v>1.05402672290802</v>
+        <v>1.05402684211731</v>
       </c>
       <c r="H875" t="n">
         <v>6443127</v>
@@ -25773,7 +25773,7 @@
         <v>1.50950002670288</v>
       </c>
       <c r="G876" t="n">
-        <v>1.05020034313202</v>
+        <v>1.0502005815506</v>
       </c>
       <c r="H876" t="n">
         <v>7269640</v>
@@ -25802,7 +25802,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G877" t="n">
-        <v>1.05193972587585</v>
+        <v>1.05193960666656</v>
       </c>
       <c r="H877" t="n">
         <v>4462576</v>
@@ -25831,7 +25831,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G878" t="n">
-        <v>1.0456782579422</v>
+        <v>1.04567813873291</v>
       </c>
       <c r="H878" t="n">
         <v>7679598</v>
@@ -25918,7 +25918,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G881" t="n">
-        <v>1.07420289516449</v>
+        <v>1.07420301437378</v>
       </c>
       <c r="H881" t="n">
         <v>10299322</v>
@@ -25976,7 +25976,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G883" t="n">
-        <v>1.09507465362549</v>
+        <v>1.09507477283478</v>
       </c>
       <c r="H883" t="n">
         <v>17350310</v>
@@ -26034,7 +26034,7 @@
         <v>1.53550004959106</v>
       </c>
       <c r="G885" t="n">
-        <v>1.06828939914703</v>
+        <v>1.06828927993774</v>
       </c>
       <c r="H885" t="n">
         <v>6576892</v>
@@ -26092,7 +26092,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G887" t="n">
-        <v>1.05333137512207</v>
+        <v>1.05333113670349</v>
       </c>
       <c r="H887" t="n">
         <v>4982314</v>
@@ -26121,7 +26121,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G888" t="n">
-        <v>1.06167995929718</v>
+        <v>1.06167984008789</v>
       </c>
       <c r="H888" t="n">
         <v>6510754</v>
@@ -26150,7 +26150,7 @@
         <v>1.52349996566772</v>
       </c>
       <c r="G889" t="n">
-        <v>1.05994057655334</v>
+        <v>1.05994045734406</v>
       </c>
       <c r="H889" t="n">
         <v>6133111</v>
@@ -26179,7 +26179,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G890" t="n">
-        <v>1.08324754238129</v>
+        <v>1.083247423172</v>
       </c>
       <c r="H890" t="n">
         <v>12371226</v>
@@ -26237,7 +26237,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G892" t="n">
-        <v>1.09924912452698</v>
+        <v>1.09924924373627</v>
       </c>
       <c r="H892" t="n">
         <v>9140449</v>
@@ -26353,7 +26353,7 @@
         <v>1.60549998283386</v>
       </c>
       <c r="G896" t="n">
-        <v>1.11699020862579</v>
+        <v>1.11699032783508</v>
       </c>
       <c r="H896" t="n">
         <v>9037328</v>
@@ -26382,7 +26382,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G897" t="n">
-        <v>1.11803388595581</v>
+        <v>1.11803376674652</v>
       </c>
       <c r="H897" t="n">
         <v>12611264</v>
@@ -26411,7 +26411,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G898" t="n">
-        <v>1.11872935295105</v>
+        <v>1.11872947216034</v>
       </c>
       <c r="H898" t="n">
         <v>9721085</v>
@@ -26440,7 +26440,7 @@
         <v>1.61650002002716</v>
       </c>
       <c r="G899" t="n">
-        <v>1.12464332580566</v>
+        <v>1.12464320659637</v>
       </c>
       <c r="H899" t="n">
         <v>8832952</v>
@@ -26469,7 +26469,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G900" t="n">
-        <v>1.11872935295105</v>
+        <v>1.11872947216034</v>
       </c>
       <c r="H900" t="n">
         <v>6693469</v>
@@ -26585,7 +26585,7 @@
         <v>1.59949994087219</v>
       </c>
       <c r="G904" t="n">
-        <v>1.1128157377243</v>
+        <v>1.11281585693359</v>
       </c>
       <c r="H904" t="n">
         <v>8058867</v>
@@ -26788,7 +26788,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G911" t="n">
-        <v>1.09924912452698</v>
+        <v>1.09924924373627</v>
       </c>
       <c r="H911" t="n">
         <v>9481223</v>
@@ -26846,7 +26846,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G913" t="n">
-        <v>1.11733818054199</v>
+        <v>1.1173380613327</v>
       </c>
       <c r="H913" t="n">
         <v>14592090</v>
@@ -26933,7 +26933,7 @@
         <v>1.60150003433228</v>
       </c>
       <c r="G916" t="n">
-        <v>1.11420726776123</v>
+        <v>1.11420738697052</v>
       </c>
       <c r="H916" t="n">
         <v>8470006</v>
@@ -26962,7 +26962,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>1.11664223670959</v>
+        <v>1.11664235591888</v>
       </c>
       <c r="H917" t="n">
         <v>6290940</v>
@@ -27020,7 +27020,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G919" t="n">
-        <v>1.07281172275543</v>
+        <v>1.07281148433685</v>
       </c>
       <c r="H919" t="n">
         <v>8138628</v>
@@ -27165,7 +27165,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G924" t="n">
-        <v>1.09229207038879</v>
+        <v>1.0922919511795</v>
       </c>
       <c r="H924" t="n">
         <v>4336554</v>
@@ -27194,7 +27194,7 @@
         <v>1.58150005340576</v>
       </c>
       <c r="G925" t="n">
-        <v>1.10029268264771</v>
+        <v>1.10029280185699</v>
       </c>
       <c r="H925" t="n">
         <v>5213972</v>
@@ -27281,7 +27281,7 @@
         <v>1.55649995803833</v>
       </c>
       <c r="G928" t="n">
-        <v>1.0828994512558</v>
+        <v>1.08289957046509</v>
       </c>
       <c r="H928" t="n">
         <v>4059248</v>
@@ -27310,7 +27310,7 @@
         <v>1.59650003910065</v>
       </c>
       <c r="G929" t="n">
-        <v>1.11072874069214</v>
+        <v>1.11072862148285</v>
       </c>
       <c r="H929" t="n">
         <v>5963740</v>
@@ -27339,7 +27339,7 @@
         <v>1.59949994087219</v>
       </c>
       <c r="G930" t="n">
-        <v>1.1128157377243</v>
+        <v>1.11281585693359</v>
       </c>
       <c r="H930" t="n">
         <v>10035917</v>
@@ -27368,7 +27368,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G931" t="n">
-        <v>1.11594665050507</v>
+        <v>1.11594653129578</v>
       </c>
       <c r="H931" t="n">
         <v>6473932</v>
@@ -27397,7 +27397,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G932" t="n">
-        <v>1.1124678850174</v>
+        <v>1.11246800422668</v>
       </c>
       <c r="H932" t="n">
         <v>7033825</v>
@@ -27426,7 +27426,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G933" t="n">
-        <v>1.11177241802216</v>
+        <v>1.11177229881287</v>
       </c>
       <c r="H933" t="n">
         <v>3790758</v>
@@ -27455,7 +27455,7 @@
         <v>1.59650003910065</v>
       </c>
       <c r="G934" t="n">
-        <v>1.11072874069214</v>
+        <v>1.11072862148285</v>
       </c>
       <c r="H934" t="n">
         <v>3838227</v>
@@ -27484,7 +27484,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G935" t="n">
-        <v>1.1340354681015</v>
+        <v>1.13403534889221</v>
       </c>
       <c r="H935" t="n">
         <v>7961147</v>
@@ -27571,7 +27571,7 @@
         <v>1.630499958992</v>
       </c>
       <c r="G938" t="n">
-        <v>1.13438332080841</v>
+        <v>1.1343834400177</v>
       </c>
       <c r="H938" t="n">
         <v>6266794</v>
@@ -27658,7 +27658,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G941" t="n">
-        <v>1.1340354681015</v>
+        <v>1.13403534889221</v>
       </c>
       <c r="H941" t="n">
         <v>11986314</v>
@@ -27716,7 +27716,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.11664223670959</v>
+        <v>1.11664235591888</v>
       </c>
       <c r="H943" t="n">
         <v>12492722</v>
@@ -27745,7 +27745,7 @@
         <v>1.5974999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.11142444610596</v>
+        <v>1.11142432689667</v>
       </c>
       <c r="H944" t="n">
         <v>10922511</v>
@@ -27803,7 +27803,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G946" t="n">
-        <v>1.11803388595581</v>
+        <v>1.11803376674652</v>
       </c>
       <c r="H946" t="n">
         <v>9196109</v>
@@ -27861,7 +27861,7 @@
         <v>1.61349999904633</v>
       </c>
       <c r="G948" t="n">
-        <v>1.12255609035492</v>
+        <v>1.12255597114563</v>
       </c>
       <c r="H948" t="n">
         <v>6130286</v>
@@ -27890,7 +27890,7 @@
         <v>1.64049994945526</v>
       </c>
       <c r="G949" t="n">
-        <v>1.14134061336517</v>
+        <v>1.14134049415588</v>
       </c>
       <c r="H949" t="n">
         <v>13217430</v>
@@ -27919,7 +27919,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G950" t="n">
-        <v>1.13542687892914</v>
+        <v>1.13542699813843</v>
       </c>
       <c r="H950" t="n">
         <v>9353217</v>
@@ -27948,7 +27948,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G951" t="n">
-        <v>1.16951775550842</v>
+        <v>1.16951763629913</v>
       </c>
       <c r="H951" t="n">
         <v>11938940</v>
@@ -27977,7 +27977,7 @@
         <v>1.66750001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>1.16012525558472</v>
+        <v>1.16012537479401</v>
       </c>
       <c r="H952" t="n">
         <v>15645537</v>
@@ -28006,7 +28006,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G953" t="n">
-        <v>1.17160487174988</v>
+        <v>1.17160475254059</v>
       </c>
       <c r="H953" t="n">
         <v>9485498</v>
@@ -28035,7 +28035,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G954" t="n">
-        <v>1.17577922344208</v>
+        <v>1.17577910423279</v>
       </c>
       <c r="H954" t="n">
         <v>13725147</v>
@@ -28064,7 +28064,7 @@
         <v>1.66550004482269</v>
       </c>
       <c r="G955" t="n">
-        <v>1.15873384475708</v>
+        <v>1.15873396396637</v>
       </c>
       <c r="H955" t="n">
         <v>10245598</v>
@@ -28122,7 +28122,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G957" t="n">
-        <v>1.17508327960968</v>
+        <v>1.17508351802826</v>
       </c>
       <c r="H957" t="n">
         <v>9637276</v>
@@ -28180,7 +28180,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G959" t="n">
-        <v>1.16047298908234</v>
+        <v>1.16047322750092</v>
       </c>
       <c r="H959" t="n">
         <v>6699896</v>
@@ -28209,7 +28209,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G960" t="n">
-        <v>1.16047298908234</v>
+        <v>1.16047322750092</v>
       </c>
       <c r="H960" t="n">
         <v>6826583</v>
@@ -28238,7 +28238,7 @@
         <v>1.67250001430511</v>
       </c>
       <c r="G961" t="n">
-        <v>1.16360402107239</v>
+        <v>1.1636039018631</v>
       </c>
       <c r="H961" t="n">
         <v>8353565</v>
@@ -28267,7 +28267,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G962" t="n">
-        <v>1.18134498596191</v>
+        <v>1.18134486675262</v>
       </c>
       <c r="H962" t="n">
         <v>8917805</v>
@@ -28296,7 +28296,7 @@
         <v>1.69350004196167</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17821431159973</v>
+        <v>1.17821419239044</v>
       </c>
       <c r="H963" t="n">
         <v>5228847</v>
@@ -28354,7 +28354,7 @@
         <v>1.66849994659424</v>
       </c>
       <c r="G965" t="n">
-        <v>1.16082108020782</v>
+        <v>1.16082084178925</v>
       </c>
       <c r="H965" t="n">
         <v>11320747</v>
@@ -28383,7 +28383,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G966" t="n">
-        <v>1.16603899002075</v>
+        <v>1.16603887081146</v>
       </c>
       <c r="H966" t="n">
         <v>6135454</v>
@@ -28499,7 +28499,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>1.17230045795441</v>
+        <v>1.1723005771637</v>
       </c>
       <c r="H970" t="n">
         <v>4666154</v>
@@ -28557,7 +28557,7 @@
         <v>1.68550002574921</v>
       </c>
       <c r="G972" t="n">
-        <v>1.17264831066132</v>
+        <v>1.17264842987061</v>
       </c>
       <c r="H972" t="n">
         <v>5685302</v>
@@ -28615,7 +28615,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G974" t="n">
-        <v>1.21543574333191</v>
+        <v>1.21543562412262</v>
       </c>
       <c r="H974" t="n">
         <v>23400052</v>
@@ -28644,7 +28644,7 @@
         <v>1.75150001049042</v>
       </c>
       <c r="G975" t="n">
-        <v>1.2185662984848</v>
+        <v>1.21856641769409</v>
       </c>
       <c r="H975" t="n">
         <v>14653065</v>
@@ -28760,7 +28760,7 @@
         <v>1.79449999332428</v>
       </c>
       <c r="G979" t="n">
-        <v>1.24848258495331</v>
+        <v>1.2484827041626</v>
       </c>
       <c r="H979" t="n">
         <v>9779009</v>
@@ -28789,7 +28789,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G980" t="n">
-        <v>1.25578773021698</v>
+        <v>1.25578784942627</v>
       </c>
       <c r="H980" t="n">
         <v>13095069</v>
@@ -28818,7 +28818,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G981" t="n">
-        <v>1.23422038555145</v>
+        <v>1.23422026634216</v>
       </c>
       <c r="H981" t="n">
         <v>15885418</v>
@@ -28905,7 +28905,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G984" t="n">
-        <v>1.24883031845093</v>
+        <v>1.24883055686951</v>
       </c>
       <c r="H984" t="n">
         <v>13668575</v>
@@ -28934,7 +28934,7 @@
         <v>1.77950000762939</v>
       </c>
       <c r="G985" t="n">
-        <v>1.23804664611816</v>
+        <v>1.23804688453674</v>
       </c>
       <c r="H985" t="n">
         <v>16757117</v>
@@ -28963,7 +28963,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G986" t="n">
-        <v>1.22030568122864</v>
+        <v>1.22030556201935</v>
       </c>
       <c r="H986" t="n">
         <v>13172896</v>
@@ -28992,7 +28992,7 @@
         <v>1.76750004291534</v>
       </c>
       <c r="G987" t="n">
-        <v>1.22969794273376</v>
+        <v>1.22969806194305</v>
       </c>
       <c r="H987" t="n">
         <v>10579385</v>
@@ -29079,7 +29079,7 @@
         <v>1.74899995326996</v>
       </c>
       <c r="G990" t="n">
-        <v>1.21682703495026</v>
+        <v>1.21682691574097</v>
       </c>
       <c r="H990" t="n">
         <v>11983945</v>
@@ -29282,7 +29282,7 @@
         <v>1.70749998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.18795442581177</v>
+        <v>1.18795418739319</v>
       </c>
       <c r="H997" t="n">
         <v>7149331</v>
@@ -29311,7 +29311,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G998" t="n">
-        <v>1.13612270355225</v>
+        <v>1.13612258434296</v>
       </c>
       <c r="H998" t="n">
         <v>21688015</v>
@@ -29398,7 +29398,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.13612270355225</v>
+        <v>1.13612258434296</v>
       </c>
       <c r="H1001" t="n">
         <v>7035183</v>
@@ -29427,7 +29427,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.13890552520752</v>
+        <v>1.13890564441681</v>
       </c>
       <c r="H1002" t="n">
         <v>8238448</v>
@@ -29456,7 +29456,7 @@
         <v>1.619500041008</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.12673044204712</v>
+        <v>1.12673020362854</v>
       </c>
       <c r="H1003" t="n">
         <v>9368305</v>
@@ -29514,7 +29514,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.14725422859192</v>
+        <v>1.14725434780121</v>
       </c>
       <c r="H1005" t="n">
         <v>15520336</v>
@@ -29601,7 +29601,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.15142846107483</v>
+        <v>1.15142858028412</v>
       </c>
       <c r="H1008" t="n">
         <v>10078211</v>
@@ -29630,7 +29630,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.16603899002075</v>
+        <v>1.16603887081146</v>
       </c>
       <c r="H1009" t="n">
         <v>9433792</v>
@@ -29659,7 +29659,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.15212452411652</v>
+        <v>1.15212440490723</v>
       </c>
       <c r="H1010" t="n">
         <v>9749588</v>
@@ -29775,7 +29775,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.18134498596191</v>
+        <v>1.18134486675262</v>
       </c>
       <c r="H1014" t="n">
         <v>6945841</v>
@@ -29833,7 +29833,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.16603899002075</v>
+        <v>1.16603887081146</v>
       </c>
       <c r="H1016" t="n">
         <v>4827689</v>
@@ -29862,7 +29862,7 @@
         <v>1.66349995136261</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.15734243392944</v>
+        <v>1.15734231472015</v>
       </c>
       <c r="H1017" t="n">
         <v>8637214</v>
@@ -29891,7 +29891,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.15212452411652</v>
+        <v>1.15212440490723</v>
       </c>
       <c r="H1018" t="n">
         <v>7158649</v>
@@ -29920,7 +29920,7 @@
         <v>1.65750002861023</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.15316808223724</v>
+        <v>1.15316820144653</v>
       </c>
       <c r="H1019" t="n">
         <v>6278399</v>
@@ -29949,7 +29949,7 @@
         <v>1.68550002574921</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.17264831066132</v>
+        <v>1.17264842987061</v>
       </c>
       <c r="H1020" t="n">
         <v>10577452</v>
@@ -29978,7 +29978,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.18134498596191</v>
+        <v>1.18134486675262</v>
       </c>
       <c r="H1021" t="n">
         <v>9608454</v>
@@ -30007,7 +30007,7 @@
         <v>1.72150003910065</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.1976945400238</v>
+        <v>1.19769465923309</v>
       </c>
       <c r="H1022" t="n">
         <v>9891773</v>
@@ -30123,7 +30123,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.21056568622589</v>
+        <v>1.2105655670166</v>
       </c>
       <c r="H1026" t="n">
         <v>8615691</v>
@@ -30152,7 +30152,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.24048185348511</v>
+        <v>1.24048173427582</v>
       </c>
       <c r="H1027" t="n">
         <v>16145831</v>
@@ -30181,7 +30181,7 @@
         <v>1.78750002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.24361264705658</v>
+        <v>1.24361252784729</v>
       </c>
       <c r="H1028" t="n">
         <v>12295485</v>
@@ -30239,7 +30239,7 @@
         <v>1.77250003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.23317670822144</v>
+        <v>1.23317658901215</v>
       </c>
       <c r="H1030" t="n">
         <v>6698008</v>
@@ -30268,7 +30268,7 @@
         <v>1.79449999332428</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24848258495331</v>
+        <v>1.2484827041626</v>
       </c>
       <c r="H1031" t="n">
         <v>8443310</v>
@@ -30413,7 +30413,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.27318120002747</v>
+        <v>1.27318108081818</v>
       </c>
       <c r="H1036" t="n">
         <v>10731420</v>
@@ -30442,7 +30442,7 @@
         <v>1.80250000953674</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.25404858589172</v>
+        <v>1.25404846668243</v>
       </c>
       <c r="H1037" t="n">
         <v>13168286</v>
@@ -30587,7 +30587,7 @@
         <v>1.82650005817413</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.27074599266052</v>
+        <v>1.27074587345123</v>
       </c>
       <c r="H1042" t="n">
         <v>16630816</v>
@@ -30674,7 +30674,7 @@
         <v>1.84350001811981</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.28257322311401</v>
+        <v>1.2825733423233</v>
       </c>
       <c r="H1045" t="n">
         <v>7946466</v>
@@ -30790,7 +30790,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.30727159976959</v>
+        <v>1.30727171897888</v>
       </c>
       <c r="H1049" t="n">
         <v>6853542</v>
@@ -30819,7 +30819,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.31909894943237</v>
+        <v>1.31909906864166</v>
       </c>
       <c r="H1050" t="n">
         <v>10336851</v>
@@ -30848,7 +30848,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.29822719097137</v>
+        <v>1.29822707176208</v>
       </c>
       <c r="H1051" t="n">
         <v>8737180</v>
@@ -30877,7 +30877,7 @@
         <v>1.85049998760223</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.28744339942932</v>
+        <v>1.28744328022003</v>
       </c>
       <c r="H1052" t="n">
         <v>9223781</v>
@@ -30935,7 +30935,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.19873821735382</v>
+        <v>1.19873797893524</v>
       </c>
       <c r="H1054" t="n">
         <v>20005123</v>
@@ -30993,7 +30993,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.15212452411652</v>
+        <v>1.15212440490723</v>
       </c>
       <c r="H1056" t="n">
         <v>19109999</v>
@@ -31080,7 +31080,7 @@
         <v>1.58550000190735</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.10307574272156</v>
+        <v>1.10307562351227</v>
       </c>
       <c r="H1059" t="n">
         <v>16834990</v>
@@ -31109,7 +31109,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.1423841714859</v>
+        <v>1.14238429069519</v>
       </c>
       <c r="H1060" t="n">
         <v>19502487</v>
@@ -31138,7 +31138,7 @@
         <v>1.5974999666214</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.11142444610596</v>
+        <v>1.11142432689667</v>
       </c>
       <c r="H1061" t="n">
         <v>17083848</v>
@@ -31196,7 +31196,7 @@
         <v>1.36650002002716</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.950711369514465</v>
+        <v>0.95071142911911</v>
       </c>
       <c r="H1063" t="n">
         <v>23248026</v>
@@ -31225,7 +31225,7 @@
         <v>1.2684999704361</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.882530093193054</v>
+        <v>0.882530033588409</v>
       </c>
       <c r="H1064" t="n">
         <v>24600695</v>
@@ -31254,7 +31254,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.86409330368042</v>
+        <v>0.864093482494354</v>
       </c>
       <c r="H1065" t="n">
         <v>20875345</v>
@@ -31283,7 +31283,7 @@
         <v>1.005499958992</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.699553787708282</v>
+        <v>0.699553728103638</v>
       </c>
       <c r="H1066" t="n">
         <v>33310063</v>
@@ -31428,7 +31428,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.720077693462372</v>
+        <v>0.720077753067017</v>
       </c>
       <c r="H1071" t="n">
         <v>39191916</v>
@@ -31486,7 +31486,7 @@
         <v>1</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.695727288722992</v>
+        <v>0.695727348327637</v>
       </c>
       <c r="H1073" t="n">
         <v>20512792</v>
@@ -31573,7 +31573,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.756951332092285</v>
+        <v>0.756951451301575</v>
       </c>
       <c r="H1076" t="n">
         <v>17753248</v>
@@ -31660,7 +31660,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.788259088993073</v>
+        <v>0.788259029388428</v>
       </c>
       <c r="H1079" t="n">
         <v>21805919</v>
@@ -31718,7 +31718,7 @@
         <v>1.15450000762939</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.803217113018036</v>
+        <v>0.803217053413391</v>
       </c>
       <c r="H1081" t="n">
         <v>14237585</v>
@@ -31747,7 +31747,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.797999143600464</v>
+        <v>0.797999083995819</v>
       </c>
       <c r="H1082" t="n">
         <v>17055030</v>
@@ -31834,7 +31834,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.816088020801544</v>
+        <v>0.816088080406189</v>
       </c>
       <c r="H1085" t="n">
         <v>10870072</v>
@@ -31863,7 +31863,7 @@
         <v>1.20249998569489</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.836612045764923</v>
+        <v>0.836612164974213</v>
       </c>
       <c r="H1086" t="n">
         <v>14699921</v>
@@ -31892,7 +31892,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.848787367343903</v>
+        <v>0.848787426948547</v>
       </c>
       <c r="H1087" t="n">
         <v>13306378</v>
@@ -31921,7 +31921,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.845308601856232</v>
+        <v>0.845308721065521</v>
       </c>
       <c r="H1088" t="n">
         <v>18079844</v>
@@ -31950,7 +31950,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.856440305709839</v>
+        <v>0.856440186500549</v>
       </c>
       <c r="H1089" t="n">
         <v>16041598</v>
@@ -31979,7 +31979,7 @@
         <v>1.24950003623962</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.869311332702637</v>
+        <v>0.869311451911926</v>
       </c>
       <c r="H1090" t="n">
         <v>14850584</v>
@@ -32008,7 +32008,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.87000697851181</v>
+        <v>0.870006918907166</v>
       </c>
       <c r="H1091" t="n">
         <v>12592286</v>
@@ -32037,7 +32037,7 @@
         <v>1.21249997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.843569278717041</v>
+        <v>0.843569397926331</v>
       </c>
       <c r="H1092" t="n">
         <v>12958544</v>
@@ -32066,7 +32066,7 @@
         <v>1.21850001811981</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.84774374961853</v>
+        <v>0.847743809223175</v>
       </c>
       <c r="H1093" t="n">
         <v>9042765</v>
@@ -32095,7 +32095,7 @@
         <v>1.20650005340576</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.839395046234131</v>
+        <v>0.839395105838776</v>
       </c>
       <c r="H1094" t="n">
         <v>9165038</v>
@@ -32124,7 +32124,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.849482893943787</v>
+        <v>0.849482953548431</v>
       </c>
       <c r="H1095" t="n">
         <v>9617277</v>
@@ -32153,7 +32153,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.865484833717346</v>
+        <v>0.865484774112701</v>
       </c>
       <c r="H1096" t="n">
         <v>6501772</v>
@@ -32182,7 +32182,7 @@
         <v>1.23650002479553</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.860266745090485</v>
+        <v>0.860266804695129</v>
       </c>
       <c r="H1097" t="n">
         <v>10045347</v>
@@ -32211,7 +32211,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.858527481555939</v>
+        <v>0.858527421951294</v>
       </c>
       <c r="H1098" t="n">
         <v>12682011</v>
@@ -32240,7 +32240,7 @@
         <v>1.24249994754791</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.864441096782684</v>
+        <v>0.864441156387329</v>
       </c>
       <c r="H1099" t="n">
         <v>10305332</v>
@@ -32298,7 +32298,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.83974289894104</v>
+        <v>0.839742839336395</v>
       </c>
       <c r="H1101" t="n">
         <v>10345701</v>
@@ -32443,7 +32443,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.872790038585663</v>
+        <v>0.872789919376373</v>
       </c>
       <c r="H1106" t="n">
         <v>14086926</v>
@@ -32472,7 +32472,7 @@
         <v>1.28149998188019</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.891574621200562</v>
+        <v>0.891574501991272</v>
       </c>
       <c r="H1107" t="n">
         <v>15650952</v>
@@ -32588,7 +32588,7 @@
         <v>1.16149997711182</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.861500263214111</v>
+        <v>0.861500203609467</v>
       </c>
       <c r="H1111" t="n">
         <v>21612434</v>
@@ -32646,7 +32646,7 @@
         <v>1.17149996757507</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.868917405605316</v>
+        <v>0.868917346000671</v>
       </c>
       <c r="H1113" t="n">
         <v>8713141</v>
@@ -32675,7 +32675,7 @@
         <v>1.17449998855591</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.871142506599426</v>
+        <v>0.871142446994781</v>
       </c>
       <c r="H1114" t="n">
         <v>7729979</v>
@@ -32733,7 +32733,7 @@
         <v>1.24950003623962</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.92677116394043</v>
+        <v>0.926771223545074</v>
       </c>
       <c r="H1116" t="n">
         <v>17890525</v>
@@ -32762,7 +32762,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.907115757465363</v>
+        <v>0.907115697860718</v>
       </c>
       <c r="H1117" t="n">
         <v>13737623</v>
@@ -32791,7 +32791,7 @@
         <v>1.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.927141904830933</v>
+        <v>0.927141845226288</v>
       </c>
       <c r="H1118" t="n">
         <v>17021685</v>
@@ -32820,7 +32820,7 @@
         <v>1.24749994277954</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.92528760433197</v>
+        <v>0.925287663936615</v>
       </c>
       <c r="H1119" t="n">
         <v>15164645</v>
@@ -32849,7 +32849,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.936784088611603</v>
+        <v>0.936784267425537</v>
       </c>
       <c r="H1120" t="n">
         <v>11863807</v>
@@ -32936,7 +32936,7 @@
         <v>1.34249997138977</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.995750486850739</v>
+        <v>0.995750367641449</v>
       </c>
       <c r="H1123" t="n">
         <v>20831148</v>
@@ -33023,7 +33023,7 @@
         <v>1.32149994373322</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.980174362659454</v>
+        <v>0.980174481868744</v>
       </c>
       <c r="H1126" t="n">
         <v>17896590</v>
@@ -33081,7 +33081,7 @@
         <v>1.23549997806549</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.916386961936951</v>
+        <v>0.91638708114624</v>
       </c>
       <c r="H1128" t="n">
         <v>17893430</v>
@@ -33110,7 +33110,7 @@
         <v>1.23049998283386</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.912678420543671</v>
+        <v>0.91267853975296</v>
       </c>
       <c r="H1129" t="n">
         <v>11374260</v>
@@ -33197,7 +33197,7 @@
         <v>1.30949997901917</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.971273839473724</v>
+        <v>0.971273720264435</v>
       </c>
       <c r="H1132" t="n">
         <v>10470336</v>
@@ -33226,7 +33226,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.963485777378082</v>
+        <v>0.963485896587372</v>
       </c>
       <c r="H1133" t="n">
         <v>7368686</v>
@@ -33342,7 +33342,7 @@
         <v>1.24950003623962</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.92677116394043</v>
+        <v>0.926771223545074</v>
       </c>
       <c r="H1137" t="n">
         <v>9294659</v>
@@ -33371,7 +33371,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.927883565425873</v>
+        <v>0.927883684635162</v>
       </c>
       <c r="H1138" t="n">
         <v>16000295</v>
@@ -33400,7 +33400,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.919724762439728</v>
+        <v>0.919724822044373</v>
       </c>
       <c r="H1139" t="n">
         <v>6650541</v>
@@ -33429,7 +33429,7 @@
         <v>1.25750005245209</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.932704746723175</v>
+        <v>0.93270480632782</v>
       </c>
       <c r="H1140" t="n">
         <v>6399377</v>
@@ -33458,7 +33458,7 @@
         <v>1.26049995422363</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.934930026531219</v>
+        <v>0.934929966926575</v>
       </c>
       <c r="H1141" t="n">
         <v>9474103</v>
@@ -33516,7 +33516,7 @@
         <v>1.28649997711182</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.954214334487915</v>
+        <v>0.954214453697205</v>
       </c>
       <c r="H1143" t="n">
         <v>9692557</v>
@@ -33545,7 +33545,7 @@
         <v>1.28250002861023</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.951247692108154</v>
+        <v>0.95124763250351</v>
       </c>
       <c r="H1144" t="n">
         <v>8397843</v>
@@ -33574,7 +33574,7 @@
         <v>1.27849996089935</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.948280811309814</v>
+        <v>0.948280692100525</v>
       </c>
       <c r="H1145" t="n">
         <v>6212209</v>
@@ -33603,7 +33603,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.938267648220062</v>
+        <v>0.938267707824707</v>
       </c>
       <c r="H1146" t="n">
         <v>5503663</v>
@@ -33632,7 +33632,7 @@
         <v>1.26450002193451</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.937896847724915</v>
+        <v>0.93789666891098</v>
       </c>
       <c r="H1147" t="n">
         <v>5259823</v>
@@ -33661,7 +33661,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.914532840251923</v>
+        <v>0.914532780647278</v>
       </c>
       <c r="H1148" t="n">
         <v>8037690</v>
@@ -33690,7 +33690,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.917499601840973</v>
+        <v>0.917499661445618</v>
       </c>
       <c r="H1149" t="n">
         <v>6038533</v>
@@ -33719,7 +33719,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.927883565425873</v>
+        <v>0.927883684635162</v>
       </c>
       <c r="H1150" t="n">
         <v>4656355</v>
@@ -33748,7 +33748,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.917499601840973</v>
+        <v>0.917499661445618</v>
       </c>
       <c r="H1151" t="n">
         <v>7319561</v>
@@ -33777,7 +33777,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.916757941246033</v>
+        <v>0.916757881641388</v>
       </c>
       <c r="H1152" t="n">
         <v>12026634</v>
@@ -33806,7 +33806,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.929367065429688</v>
+        <v>0.929367005825043</v>
       </c>
       <c r="H1153" t="n">
         <v>8225773</v>
@@ -33835,7 +33835,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.928625464439392</v>
+        <v>0.928625285625458</v>
       </c>
       <c r="H1154" t="n">
         <v>9457610</v>
@@ -33864,7 +33864,7 @@
         <v>1.26750004291534</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.940122008323669</v>
+        <v>0.940121829509735</v>
       </c>
       <c r="H1155" t="n">
         <v>10023962</v>
@@ -33893,7 +33893,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.942717850208282</v>
+        <v>0.942717969417572</v>
       </c>
       <c r="H1156" t="n">
         <v>15024396</v>
@@ -33951,7 +33951,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.940492749214172</v>
+        <v>0.940492808818817</v>
       </c>
       <c r="H1158" t="n">
         <v>12982545</v>
@@ -33980,7 +33980,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.928625464439392</v>
+        <v>0.928625285625458</v>
       </c>
       <c r="H1159" t="n">
         <v>7590684</v>
@@ -34067,7 +34067,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.926400244235992</v>
+        <v>0.926400184631348</v>
       </c>
       <c r="H1162" t="n">
         <v>11803018</v>
@@ -34096,7 +34096,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.886347711086273</v>
+        <v>0.886347770690918</v>
       </c>
       <c r="H1163" t="n">
         <v>18467152</v>
@@ -34125,7 +34125,7 @@
         <v>1.21350002288818</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.900069355964661</v>
+        <v>0.900069296360016</v>
       </c>
       <c r="H1164" t="n">
         <v>19191631</v>
@@ -34212,7 +34212,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917499601840973</v>
+        <v>0.917499661445618</v>
       </c>
       <c r="H1167" t="n">
         <v>7740379</v>
@@ -34241,7 +34241,7 @@
         <v>1.22699999809265</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.910082519054413</v>
+        <v>0.910082399845123</v>
       </c>
       <c r="H1168" t="n">
         <v>8546929</v>
@@ -34270,7 +34270,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.921208143234253</v>
+        <v>0.921208322048187</v>
       </c>
       <c r="H1169" t="n">
         <v>11131761</v>
@@ -34357,7 +34357,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.970903158187866</v>
+        <v>0.970903038978577</v>
       </c>
       <c r="H1172" t="n">
         <v>8935682</v>
@@ -34415,7 +34415,7 @@
         <v>1.27849996089935</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.948280811309814</v>
+        <v>0.948280692100525</v>
       </c>
       <c r="H1174" t="n">
         <v>5945069</v>
@@ -34444,7 +34444,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.949393391609192</v>
+        <v>0.949393272399902</v>
       </c>
       <c r="H1175" t="n">
         <v>5333084</v>
@@ -34502,7 +34502,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.944201290607452</v>
+        <v>0.944201350212097</v>
       </c>
       <c r="H1177" t="n">
         <v>8295550</v>
@@ -34531,7 +34531,7 @@
         <v>1.26450002193451</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.937896847724915</v>
+        <v>0.93789666891098</v>
       </c>
       <c r="H1178" t="n">
         <v>4272198</v>
@@ -34589,7 +34589,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.949393391609192</v>
+        <v>0.949393272399902</v>
       </c>
       <c r="H1180" t="n">
         <v>7825908</v>
@@ -34618,7 +34618,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.941976189613342</v>
+        <v>0.941976130008698</v>
       </c>
       <c r="H1181" t="n">
         <v>4378076</v>
@@ -34647,7 +34647,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.926400244235992</v>
+        <v>0.926400184631348</v>
       </c>
       <c r="H1182" t="n">
         <v>8035446</v>
@@ -34676,7 +34676,7 @@
         <v>1.24150002002716</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.92083728313446</v>
+        <v>0.920837342739105</v>
       </c>
       <c r="H1183" t="n">
         <v>8316572</v>
@@ -34705,7 +34705,7 @@
         <v>1.23849999904633</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.918612122535706</v>
+        <v>0.918612062931061</v>
       </c>
       <c r="H1184" t="n">
         <v>5435831</v>
@@ -34734,7 +34734,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.907115757465363</v>
+        <v>0.907115697860718</v>
       </c>
       <c r="H1185" t="n">
         <v>11735865</v>
@@ -34763,7 +34763,7 @@
         <v>1.2335000038147</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.914903581142426</v>
+        <v>0.91490364074707</v>
       </c>
       <c r="H1186" t="n">
         <v>7491586</v>
@@ -34792,7 +34792,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.919724762439728</v>
+        <v>0.919724822044373</v>
       </c>
       <c r="H1187" t="n">
         <v>9446560</v>
@@ -34850,7 +34850,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.907857179641724</v>
+        <v>0.907857358455658</v>
       </c>
       <c r="H1189" t="n">
         <v>11077063</v>
@@ -34937,7 +34937,7 @@
         <v>1.25450003147125</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.93047970533371</v>
+        <v>0.930479645729065</v>
       </c>
       <c r="H1192" t="n">
         <v>8395532</v>
@@ -34966,7 +34966,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.914532840251923</v>
+        <v>0.914532780647278</v>
       </c>
       <c r="H1193" t="n">
         <v>9705867</v>
@@ -34995,7 +34995,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.919724762439728</v>
+        <v>0.919724822044373</v>
       </c>
       <c r="H1194" t="n">
         <v>6708910</v>
@@ -35024,7 +35024,7 @@
         <v>1.2335000038147</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.914903581142426</v>
+        <v>0.91490364074707</v>
       </c>
       <c r="H1195" t="n">
         <v>5094421</v>
@@ -35111,7 +35111,7 @@
         <v>1.26450002193451</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937896847724915</v>
+        <v>0.93789666891098</v>
       </c>
       <c r="H1198" t="n">
         <v>15062931</v>
@@ -35140,7 +35140,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.917499601840973</v>
+        <v>0.917499661445618</v>
       </c>
       <c r="H1199" t="n">
         <v>14722464</v>
@@ -35169,7 +35169,7 @@
         <v>1.20650005340576</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.894877374172211</v>
+        <v>0.894877433776855</v>
       </c>
       <c r="H1200" t="n">
         <v>13294895</v>
@@ -35198,7 +35198,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.903407096862793</v>
+        <v>0.903407156467438</v>
       </c>
       <c r="H1201" t="n">
         <v>8112659</v>
@@ -35227,7 +35227,7 @@
         <v>1.20749998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.895619034767151</v>
+        <v>0.895619094371796</v>
       </c>
       <c r="H1202" t="n">
         <v>5426899</v>
@@ -35285,7 +35285,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.890797913074493</v>
+        <v>0.890797972679138</v>
       </c>
       <c r="H1204" t="n">
         <v>7786502</v>
@@ -35314,7 +35314,7 @@
         <v>1.25049996376038</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.92751270532608</v>
+        <v>0.927512764930725</v>
       </c>
       <c r="H1205" t="n">
         <v>12068681</v>
@@ -35343,7 +35343,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.927883565425873</v>
+        <v>0.927883684635162</v>
       </c>
       <c r="H1206" t="n">
         <v>13082035</v>
@@ -35372,7 +35372,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.919724762439728</v>
+        <v>0.919724822044373</v>
       </c>
       <c r="H1207" t="n">
         <v>7820034</v>
@@ -35430,7 +35430,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.914532840251923</v>
+        <v>0.914532780647278</v>
       </c>
       <c r="H1209" t="n">
         <v>5523185</v>
@@ -35459,7 +35459,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.921208143234253</v>
+        <v>0.921208322048187</v>
       </c>
       <c r="H1210" t="n">
         <v>4127631</v>
@@ -35488,7 +35488,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.917499601840973</v>
+        <v>0.917499661445618</v>
       </c>
       <c r="H1211" t="n">
         <v>4502630</v>
@@ -35517,7 +35517,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.905632138252258</v>
+        <v>0.905632078647614</v>
       </c>
       <c r="H1212" t="n">
         <v>8940886</v>
@@ -35575,7 +35575,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.907115757465363</v>
+        <v>0.907115697860718</v>
       </c>
       <c r="H1214" t="n">
         <v>7308733</v>
@@ -35691,7 +35691,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.859646022319794</v>
+        <v>0.859645962715149</v>
       </c>
       <c r="H1218" t="n">
         <v>15139773</v>
@@ -35720,7 +35720,7 @@
         <v>1.16250002384186</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.862242043018341</v>
+        <v>0.862241983413696</v>
       </c>
       <c r="H1219" t="n">
         <v>12588165</v>
@@ -35749,7 +35749,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.863354623317719</v>
+        <v>0.863354504108429</v>
       </c>
       <c r="H1220" t="n">
         <v>7297977</v>
@@ -35807,7 +35807,7 @@
         <v>1.130499958992</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.838507056236267</v>
+        <v>0.838507175445557</v>
       </c>
       <c r="H1222" t="n">
         <v>10894227</v>
@@ -35865,7 +35865,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.860387682914734</v>
+        <v>0.860387742519379</v>
       </c>
       <c r="H1224" t="n">
         <v>5586554</v>
@@ -35894,7 +35894,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.845553278923035</v>
+        <v>0.845553398132324</v>
       </c>
       <c r="H1225" t="n">
         <v>6354644</v>
@@ -35923,7 +35923,7 @@
         <v>1.130499958992</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.838507056236267</v>
+        <v>0.838507175445557</v>
       </c>
       <c r="H1226" t="n">
         <v>7777252</v>
@@ -35952,7 +35952,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.802533984184265</v>
+        <v>0.80253404378891</v>
       </c>
       <c r="H1227" t="n">
         <v>15519098</v>
@@ -36010,7 +36010,7 @@
         <v>1.09150004386902</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.809580266475677</v>
+        <v>0.809580326080322</v>
       </c>
       <c r="H1229" t="n">
         <v>7723352</v>
@@ -36097,7 +36097,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.857420802116394</v>
+        <v>0.857420861721039</v>
       </c>
       <c r="H1232" t="n">
         <v>13367473</v>
@@ -36126,7 +36126,7 @@
         <v>1.14849996566772</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.851857960224152</v>
+        <v>0.851857900619507</v>
       </c>
       <c r="H1233" t="n">
         <v>12647176</v>
@@ -36155,7 +36155,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.84110301733017</v>
+        <v>0.841103076934814</v>
       </c>
       <c r="H1234" t="n">
         <v>6099982</v>
@@ -36184,7 +36184,7 @@
         <v>1.21300005912781</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.899698555469513</v>
+        <v>0.899698495864868</v>
       </c>
       <c r="H1235" t="n">
         <v>21018873</v>
@@ -36213,7 +36213,7 @@
         <v>1.20850002765656</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.896360814571381</v>
+        <v>0.89636093378067</v>
       </c>
       <c r="H1236" t="n">
         <v>14808957</v>
@@ -36242,7 +36242,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.911565840244293</v>
+        <v>0.911565899848938</v>
       </c>
       <c r="H1237" t="n">
         <v>12669916</v>
@@ -36271,7 +36271,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.903407096862793</v>
+        <v>0.903407156467438</v>
       </c>
       <c r="H1238" t="n">
         <v>11607553</v>
@@ -36300,7 +36300,7 @@
         <v>1.22549998760223</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.908969938755035</v>
+        <v>0.908969879150391</v>
       </c>
       <c r="H1239" t="n">
         <v>10104048</v>
@@ -36329,7 +36329,7 @@
         <v>1.2335000038147</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.914903581142426</v>
+        <v>0.91490364074707</v>
       </c>
       <c r="H1240" t="n">
         <v>13753526</v>
@@ -36387,7 +36387,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.904148876667023</v>
+        <v>0.904148757457733</v>
       </c>
       <c r="H1242" t="n">
         <v>10602904</v>
@@ -36416,7 +36416,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.908599197864532</v>
+        <v>0.908599078655243</v>
       </c>
       <c r="H1243" t="n">
         <v>10277277</v>
@@ -36445,7 +36445,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.908599197864532</v>
+        <v>0.908599078655243</v>
       </c>
       <c r="H1244" t="n">
         <v>8028115</v>
@@ -36532,7 +36532,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.931592226028442</v>
+        <v>0.931592106819153</v>
       </c>
       <c r="H1247" t="n">
         <v>16748585</v>
@@ -36619,7 +36619,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.947909951210022</v>
+        <v>0.947909891605377</v>
       </c>
       <c r="H1250" t="n">
         <v>14250319</v>
@@ -36677,7 +36677,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.930850565433502</v>
+        <v>0.930850505828857</v>
       </c>
       <c r="H1252" t="n">
         <v>11729728</v>
@@ -36735,7 +36735,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.951618492603302</v>
+        <v>0.951618432998657</v>
       </c>
       <c r="H1254" t="n">
         <v>12546169</v>
@@ -36764,7 +36764,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.945684611797333</v>
+        <v>0.945684731006622</v>
       </c>
       <c r="H1255" t="n">
         <v>9297290</v>
@@ -36793,7 +36793,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.936784088611603</v>
+        <v>0.936784267425537</v>
       </c>
       <c r="H1256" t="n">
         <v>7867097</v>
@@ -36880,7 +36880,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.940492749214172</v>
+        <v>0.940492808818817</v>
       </c>
       <c r="H1259" t="n">
         <v>7100699</v>
@@ -36909,7 +36909,7 @@
         <v>1.28250002861023</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.951247692108154</v>
+        <v>0.95124763250351</v>
       </c>
       <c r="H1260" t="n">
         <v>8147911</v>
@@ -36938,7 +36938,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.927883565425873</v>
+        <v>0.927883684635162</v>
       </c>
       <c r="H1261" t="n">
         <v>15413534</v>
@@ -36967,7 +36967,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.930850565433502</v>
+        <v>0.930850505828857</v>
       </c>
       <c r="H1262" t="n">
         <v>11506885</v>
@@ -36996,7 +36996,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.950135052204132</v>
+        <v>0.950135111808777</v>
       </c>
       <c r="H1263" t="n">
         <v>14191413</v>
@@ -37054,7 +37054,7 @@
         <v>1.22850000858307</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.91119509935379</v>
+        <v>0.911195039749146</v>
       </c>
       <c r="H1265" t="n">
         <v>14260830</v>
@@ -37083,7 +37083,7 @@
         <v>1.25</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.927141904830933</v>
+        <v>0.927141845226288</v>
       </c>
       <c r="H1266" t="n">
         <v>6991662</v>
@@ -37228,7 +37228,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.987220644950867</v>
+        <v>0.987220764160156</v>
       </c>
       <c r="H1271" t="n">
         <v>15930363</v>
@@ -37257,7 +37257,7 @@
         <v>1.31749999523163</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.977207660675049</v>
+        <v>0.977207541465759</v>
       </c>
       <c r="H1272" t="n">
         <v>10959889</v>
@@ -37518,7 +37518,7 @@
         <v>1.32650005817413</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.983883082866669</v>
+        <v>0.983883023262024</v>
       </c>
       <c r="H1281" t="n">
         <v>9534487</v>
@@ -37663,7 +37663,7 @@
         <v>1.34249997138977</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.995750486850739</v>
+        <v>0.995750367641449</v>
       </c>
       <c r="H1286" t="n">
         <v>14920543</v>
@@ -37721,7 +37721,7 @@
         <v>1.35549998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.00539267063141</v>
+        <v>1.00539255142212</v>
       </c>
       <c r="H1288" t="n">
         <v>13820343</v>
@@ -37837,7 +37837,7 @@
         <v>1.35549998283386</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.00539267063141</v>
+        <v>1.00539255142212</v>
       </c>
       <c r="H1292" t="n">
         <v>9543739</v>
@@ -37866,7 +37866,7 @@
         <v>1.4264999628067</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.05805432796478</v>
+        <v>1.05805420875549</v>
       </c>
       <c r="H1293" t="n">
         <v>33523916</v>
@@ -37895,7 +37895,7 @@
         <v>1.4264999628067</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.05805432796478</v>
+        <v>1.05805420875549</v>
       </c>
       <c r="H1294" t="n">
         <v>18411866</v>
@@ -37953,7 +37953,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.10144448280334</v>
+        <v>1.10144460201263</v>
       </c>
       <c r="H1296" t="n">
         <v>24722737</v>
@@ -38011,7 +38011,7 @@
         <v>1.46449995040894</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.08623933792114</v>
+        <v>1.08623945713043</v>
       </c>
       <c r="H1298" t="n">
         <v>15260096</v>
@@ -38040,7 +38040,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.09031903743744</v>
+        <v>1.09031891822815</v>
       </c>
       <c r="H1299" t="n">
         <v>11613286</v>
@@ -38069,7 +38069,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.12147092819214</v>
+        <v>1.12147080898285</v>
       </c>
       <c r="H1300" t="n">
         <v>15267757</v>
@@ -38098,7 +38098,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.10886168479919</v>
+        <v>1.1088615655899</v>
       </c>
       <c r="H1301" t="n">
         <v>21872522</v>
@@ -38330,7 +38330,7 @@
         <v>1.40649998188019</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.04322016239166</v>
+        <v>1.04322004318237</v>
       </c>
       <c r="H1309" t="n">
         <v>13536832</v>
@@ -38388,7 +38388,7 @@
         <v>1.43449997901917</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.06398808956146</v>
+        <v>1.06398797035217</v>
       </c>
       <c r="H1311" t="n">
         <v>10726397</v>
@@ -38417,7 +38417,7 @@
         <v>1.42449998855591</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.05657088756561</v>
+        <v>1.05657076835632</v>
       </c>
       <c r="H1312" t="n">
         <v>7961479</v>
@@ -38533,7 +38533,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.05768358707428</v>
+        <v>1.05768346786499</v>
       </c>
       <c r="H1316" t="n">
         <v>12409181</v>
@@ -38591,7 +38591,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.07919311523438</v>
+        <v>1.07919323444366</v>
       </c>
       <c r="H1318" t="n">
         <v>9658511</v>
@@ -38620,7 +38620,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.09996104240417</v>
+        <v>1.09996116161346</v>
       </c>
       <c r="H1319" t="n">
         <v>15478384</v>
@@ -38649,7 +38649,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.09625267982483</v>
+        <v>1.09625256061554</v>
       </c>
       <c r="H1320" t="n">
         <v>9142143</v>
@@ -38707,7 +38707,7 @@
         <v>1.49650001525879</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.10997438430786</v>
+        <v>1.10997426509857</v>
       </c>
       <c r="H1322" t="n">
         <v>7672870</v>
@@ -38736,7 +38736,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.10144448280334</v>
+        <v>1.10144460201263</v>
       </c>
       <c r="H1323" t="n">
         <v>10401363</v>
@@ -38765,7 +38765,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.0932856798172</v>
+        <v>1.09328579902649</v>
       </c>
       <c r="H1324" t="n">
         <v>13423234</v>
@@ -38823,7 +38823,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.09402751922607</v>
+        <v>1.09402740001678</v>
       </c>
       <c r="H1326" t="n">
         <v>9601079</v>
@@ -38939,7 +38939,7 @@
         <v>1.55250000953674</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.15151035785675</v>
+        <v>1.15151023864746</v>
       </c>
       <c r="H1330" t="n">
         <v>11868816</v>
@@ -38997,7 +38997,7 @@
         <v>1.56649994850159</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16189408302307</v>
+        <v>1.16189420223236</v>
       </c>
       <c r="H1332" t="n">
         <v>12790889</v>
@@ -39026,7 +39026,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.15113925933838</v>
+        <v>1.15113937854767</v>
       </c>
       <c r="H1333" t="n">
         <v>10211662</v>
@@ -39055,7 +39055,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.14891409873962</v>
+        <v>1.14891421794891</v>
       </c>
       <c r="H1334" t="n">
         <v>9564739</v>
@@ -39113,7 +39113,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.16819870471954</v>
+        <v>1.16819882392883</v>
       </c>
       <c r="H1336" t="n">
         <v>11325487</v>
@@ -39142,7 +39142,7 @@
         <v>1.55649995803833</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.15447700023651</v>
+        <v>1.1544771194458</v>
       </c>
       <c r="H1337" t="n">
         <v>13223567</v>
@@ -39229,7 +39229,7 @@
         <v>1.56449997425079</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.16041076183319</v>
+        <v>1.16041088104248</v>
       </c>
       <c r="H1340" t="n">
         <v>15283186</v>
@@ -39287,7 +39287,7 @@
         <v>1.54949998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.14928531646729</v>
+        <v>1.149285197258</v>
       </c>
       <c r="H1342" t="n">
         <v>13293627</v>
@@ -39432,7 +39432,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.17932438850403</v>
+        <v>1.17932450771332</v>
       </c>
       <c r="H1347" t="n">
         <v>11793070</v>
@@ -39490,7 +39490,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.17932438850403</v>
+        <v>1.17932450771332</v>
       </c>
       <c r="H1349" t="n">
         <v>7060181</v>
@@ -39635,7 +39635,7 @@
         <v>1.6414999961853</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.21752285957336</v>
+        <v>1.21752274036407</v>
       </c>
       <c r="H1354" t="n">
         <v>9040711</v>
@@ -39664,7 +39664,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.20305931568146</v>
+        <v>1.20305943489075</v>
       </c>
       <c r="H1355" t="n">
         <v>11928729</v>
@@ -39780,7 +39780,7 @@
         <v>1.69550001621246</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.25757527351379</v>
+        <v>1.2575751543045</v>
       </c>
       <c r="H1359" t="n">
         <v>10581836</v>
@@ -39809,7 +39809,7 @@
         <v>1.66349995136261</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.23384046554565</v>
+        <v>1.23384034633636</v>
       </c>
       <c r="H1360" t="n">
         <v>19055804</v>
@@ -39954,7 +39954,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.28242266178131</v>
+        <v>1.28242254257202</v>
       </c>
       <c r="H1365" t="n">
         <v>16935515</v>
@@ -40041,7 +40041,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.30986618995667</v>
+        <v>1.30986607074738</v>
       </c>
       <c r="H1368" t="n">
         <v>17744717</v>
@@ -40128,7 +40128,7 @@
         <v>1.69749999046326</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.31880056858063</v>
+        <v>1.31880044937134</v>
       </c>
       <c r="H1371" t="n">
         <v>10391827</v>
@@ -40157,7 +40157,7 @@
         <v>1.69249999523163</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.31491589546204</v>
+        <v>1.31491601467133</v>
       </c>
       <c r="H1372" t="n">
         <v>9866606</v>
@@ -40273,7 +40273,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.33084261417389</v>
+        <v>1.33084273338318</v>
       </c>
       <c r="H1376" t="n">
         <v>10426310</v>
@@ -40418,7 +40418,7 @@
         <v>1.79149997234344</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.39182984828949</v>
+        <v>1.3918297290802</v>
       </c>
       <c r="H1381" t="n">
         <v>13004863</v>
@@ -40447,7 +40447,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.37279546260834</v>
+        <v>1.37279558181763</v>
       </c>
       <c r="H1382" t="n">
         <v>12226147</v>
@@ -40476,7 +40476,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.37201881408691</v>
+        <v>1.37201869487762</v>
       </c>
       <c r="H1383" t="n">
         <v>9384276</v>
@@ -40505,7 +40505,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.38289535045624</v>
+        <v>1.38289523124695</v>
       </c>
       <c r="H1384" t="n">
         <v>10689870</v>
@@ -40534,7 +40534,7 @@
         <v>1.78050005435944</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.38328385353088</v>
+        <v>1.38328397274017</v>
       </c>
       <c r="H1385" t="n">
         <v>6919001</v>
@@ -40563,7 +40563,7 @@
         <v>1.79149997234344</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.39182984828949</v>
+        <v>1.3918297290802</v>
       </c>
       <c r="H1386" t="n">
         <v>12287035</v>
@@ -40621,7 +40621,7 @@
         <v>1.79050004482269</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.39105308055878</v>
+        <v>1.39105296134949</v>
       </c>
       <c r="H1388" t="n">
         <v>23458952</v>
@@ -40679,7 +40679,7 @@
         <v>1.78050005435944</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.38328385353088</v>
+        <v>1.38328397274017</v>
       </c>
       <c r="H1390" t="n">
         <v>8766328</v>
@@ -40766,7 +40766,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.37823390960693</v>
+        <v>1.37823402881622</v>
       </c>
       <c r="H1393" t="n">
         <v>4587106</v>
@@ -40795,7 +40795,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.36191880702972</v>
+        <v>1.36191892623901</v>
       </c>
       <c r="H1394" t="n">
         <v>7633939</v>
@@ -40824,7 +40824,7 @@
         <v>1.74249994754791</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.35376143455505</v>
+        <v>1.35376131534576</v>
       </c>
       <c r="H1395" t="n">
         <v>5239525</v>
@@ -40882,7 +40882,7 @@
         <v>1.73549997806549</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.34832310676575</v>
+        <v>1.34832298755646</v>
       </c>
       <c r="H1397" t="n">
         <v>5638177</v>
@@ -40911,7 +40911,7 @@
         <v>1.74049997329712</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.35220742225647</v>
+        <v>1.35220754146576</v>
       </c>
       <c r="H1398" t="n">
         <v>4886681</v>
@@ -40969,7 +40969,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.34871137142181</v>
+        <v>1.3487114906311</v>
       </c>
       <c r="H1400" t="n">
         <v>5139985</v>
@@ -41201,7 +41201,7 @@
         <v>1.72150003910065</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.33744645118713</v>
+        <v>1.33744633197784</v>
       </c>
       <c r="H1408" t="n">
         <v>5023012</v>
@@ -41317,7 +41317,7 @@
         <v>1.71449995040894</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.33200800418854</v>
+        <v>1.33200788497925</v>
       </c>
       <c r="H1412" t="n">
         <v>5495331</v>
@@ -41375,7 +41375,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.37279546260834</v>
+        <v>1.37279558181763</v>
       </c>
       <c r="H1414" t="n">
         <v>5895107</v>
@@ -41433,7 +41433,7 @@
         <v>1.81449997425079</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.4096987247467</v>
+        <v>1.40969884395599</v>
       </c>
       <c r="H1416" t="n">
         <v>14124925</v>
@@ -41462,7 +41462,7 @@
         <v>1.81550002098083</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.410475730896</v>
+        <v>1.41047561168671</v>
       </c>
       <c r="H1417" t="n">
         <v>7101880</v>
@@ -41491,7 +41491,7 @@
         <v>1.79050004482269</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.39105308055878</v>
+        <v>1.39105296134949</v>
       </c>
       <c r="H1418" t="n">
         <v>9898936</v>
@@ -41520,7 +41520,7 @@
         <v>1.81050002574921</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.4065910577774</v>
+        <v>1.40659117698669</v>
       </c>
       <c r="H1419" t="n">
         <v>8668684</v>
@@ -41549,7 +41549,7 @@
         <v>1.80649995803833</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.40348339080811</v>
+        <v>1.4034835100174</v>
       </c>
       <c r="H1420" t="n">
         <v>3815369</v>
@@ -41694,7 +41694,7 @@
         <v>1.83449995517731</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.42523682117462</v>
+        <v>1.42523670196533</v>
       </c>
       <c r="H1425" t="n">
         <v>7431270</v>
@@ -41897,7 +41897,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.51419293880463</v>
+        <v>1.51419281959534</v>
       </c>
       <c r="H1432" t="n">
         <v>12235024</v>
@@ -42042,7 +42042,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.45747876167297</v>
+        <v>1.45747864246368</v>
       </c>
       <c r="H1437" t="n">
         <v>6649964</v>
@@ -42100,7 +42100,7 @@
         <v>1.869500041008</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.45242869853973</v>
+        <v>1.45242857933044</v>
       </c>
       <c r="H1439" t="n">
         <v>4615329</v>
@@ -42129,7 +42129,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.44504809379578</v>
+        <v>1.44504797458649</v>
       </c>
       <c r="H1440" t="n">
         <v>8730096</v>
@@ -42187,7 +42187,7 @@
         <v>1.85049998760223</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.43766736984253</v>
+        <v>1.43766725063324</v>
       </c>
       <c r="H1442" t="n">
         <v>6122106</v>
@@ -42216,7 +42216,7 @@
         <v>1.83949995040894</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.42912137508392</v>
+        <v>1.42912149429321</v>
       </c>
       <c r="H1443" t="n">
         <v>5716512</v>
@@ -42274,7 +42274,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.42484855651855</v>
+        <v>1.42484843730927</v>
       </c>
       <c r="H1445" t="n">
         <v>5115100</v>
@@ -42448,7 +42448,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.36269593238831</v>
+        <v>1.36269581317902</v>
       </c>
       <c r="H1451" t="n">
         <v>20202035</v>
@@ -42477,7 +42477,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.38522601127625</v>
+        <v>1.38522613048553</v>
       </c>
       <c r="H1452" t="n">
         <v>10492817</v>
@@ -42854,7 +42854,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.41941022872925</v>
+        <v>1.41941010951996</v>
       </c>
       <c r="H1465" t="n">
         <v>11092554</v>
@@ -42883,7 +42883,7 @@
         <v>1.82449996471405</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.41746771335602</v>
+        <v>1.41746783256531</v>
       </c>
       <c r="H1466" t="n">
         <v>10407503</v>
@@ -42912,7 +42912,7 @@
         <v>1.8474999666214</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.43533658981323</v>
+        <v>1.43533670902252</v>
       </c>
       <c r="H1467" t="n">
         <v>11045644</v>
@@ -42941,7 +42941,7 @@
         <v>1.79849994182587</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.3972681760788</v>
+        <v>1.39726829528809</v>
       </c>
       <c r="H1468" t="n">
         <v>13795774</v>
@@ -42970,7 +42970,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.37901103496552</v>
+        <v>1.37901091575623</v>
       </c>
       <c r="H1469" t="n">
         <v>7298931</v>
@@ -42999,7 +42999,7 @@
         <v>1.81149995326996</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.4073680639267</v>
+        <v>1.40736794471741</v>
       </c>
       <c r="H1470" t="n">
         <v>9622006</v>
@@ -43057,7 +43057,7 @@
         <v>1.85350000858307</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.43999803066254</v>
+        <v>1.43999814987183</v>
       </c>
       <c r="H1472" t="n">
         <v>7447305</v>
@@ -43086,7 +43086,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.43339443206787</v>
+        <v>1.43339431285858</v>
       </c>
       <c r="H1473" t="n">
         <v>8136390</v>
@@ -43144,7 +43144,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.43494820594788</v>
+        <v>1.43494832515717</v>
       </c>
       <c r="H1475" t="n">
         <v>5416918</v>
@@ -43173,7 +43173,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.45980942249298</v>
+        <v>1.45980930328369</v>
       </c>
       <c r="H1476" t="n">
         <v>9596803</v>
@@ -43260,7 +43260,7 @@
         <v>1.91250002384186</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.48583579063416</v>
+        <v>1.48583567142487</v>
       </c>
       <c r="H1479" t="n">
         <v>6360351</v>
@@ -43347,7 +43347,7 @@
         <v>1.85150003433228</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.43844437599182</v>
+        <v>1.43844449520111</v>
       </c>
       <c r="H1482" t="n">
         <v>11781905</v>
@@ -43376,7 +43376,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.41241800785065</v>
+        <v>1.41241788864136</v>
       </c>
       <c r="H1483" t="n">
         <v>8183369</v>
@@ -43521,7 +43521,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.44116353988647</v>
+        <v>1.44116342067719</v>
       </c>
       <c r="H1488" t="n">
         <v>7887364</v>
@@ -43579,7 +43579,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.41008734703064</v>
+        <v>1.41008722782135</v>
       </c>
       <c r="H1490" t="n">
         <v>6907562</v>
@@ -43666,7 +43666,7 @@
         <v>1.85350000858307</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.43999803066254</v>
+        <v>1.43999814987183</v>
       </c>
       <c r="H1493" t="n">
         <v>10873623</v>
@@ -43782,7 +43782,7 @@
         <v>1.8474999666214</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.43533658981323</v>
+        <v>1.43533670902252</v>
       </c>
       <c r="H1497" t="n">
         <v>4906503</v>
@@ -43869,7 +43869,7 @@
         <v>1.81050002574921</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.4065910577774</v>
+        <v>1.40659117698669</v>
       </c>
       <c r="H1500" t="n">
         <v>4767178</v>
@@ -43956,7 +43956,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.32851183414459</v>
+        <v>1.32851195335388</v>
       </c>
       <c r="H1503" t="n">
         <v>13543518</v>
@@ -43985,7 +43985,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.34171938896179</v>
+        <v>1.3417192697525</v>
       </c>
       <c r="H1504" t="n">
         <v>5903392</v>
@@ -44014,7 +44014,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.34171938896179</v>
+        <v>1.3417192697525</v>
       </c>
       <c r="H1505" t="n">
         <v>12932982</v>
@@ -44043,7 +44043,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36269593238831</v>
+        <v>1.36269581317902</v>
       </c>
       <c r="H1506" t="n">
         <v>7082577</v>
@@ -44072,7 +44072,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.33161962032318</v>
+        <v>1.33161950111389</v>
       </c>
       <c r="H1507" t="n">
         <v>6051660</v>
@@ -44159,7 +44159,7 @@
         <v>1.78349995613098</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.38561451435089</v>
+        <v>1.38561463356018</v>
       </c>
       <c r="H1510" t="n">
         <v>6411876</v>
@@ -44304,7 +44304,7 @@
         <v>1.79050004482269</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.39105308055878</v>
+        <v>1.39105296134949</v>
       </c>
       <c r="H1515" t="n">
         <v>5996192</v>
@@ -44362,7 +44362,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.32773506641388</v>
+        <v>1.32773494720459</v>
       </c>
       <c r="H1517" t="n">
         <v>22008045</v>
@@ -44391,7 +44391,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.30986618995667</v>
+        <v>1.30986607074738</v>
       </c>
       <c r="H1518" t="n">
         <v>15869358</v>
@@ -44420,7 +44420,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.26635921001434</v>
+        <v>1.26635932922363</v>
       </c>
       <c r="H1519" t="n">
         <v>12730771</v>
@@ -44507,7 +44507,7 @@
         <v>1.68050003051758</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.30559325218201</v>
+        <v>1.30559313297272</v>
       </c>
       <c r="H1522" t="n">
         <v>5499006</v>
@@ -44594,7 +44594,7 @@
         <v>1.71650004386902</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.33356177806854</v>
+        <v>1.33356189727783</v>
       </c>
       <c r="H1525" t="n">
         <v>4697371</v>
@@ -44623,7 +44623,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.33628106117249</v>
+        <v>1.3362809419632</v>
       </c>
       <c r="H1526" t="n">
         <v>4056614</v>
@@ -44797,7 +44797,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.29743552207947</v>
+        <v>1.29743564128876</v>
       </c>
       <c r="H1532" t="n">
         <v>6868966</v>
@@ -45116,7 +45116,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.27179753780365</v>
+        <v>1.27179765701294</v>
       </c>
       <c r="H1543" t="n">
         <v>29391995</v>
@@ -45145,7 +45145,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.30287373065948</v>
+        <v>1.30287384986877</v>
       </c>
       <c r="H1544" t="n">
         <v>15729062</v>
@@ -45261,7 +45261,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.31608128547668</v>
+        <v>1.31608140468597</v>
       </c>
       <c r="H1548" t="n">
         <v>7477558</v>
@@ -45290,7 +45290,7 @@
         <v>1.69050002098083</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.31336236000061</v>
+        <v>1.31336224079132</v>
       </c>
       <c r="H1549" t="n">
         <v>12415795</v>
@@ -45377,7 +45377,7 @@
         <v>1.6085000038147</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.24965584278107</v>
+        <v>1.24965572357178</v>
       </c>
       <c r="H1552" t="n">
         <v>12936698</v>
@@ -45522,7 +45522,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.20653748512268</v>
+        <v>1.20653736591339</v>
       </c>
       <c r="H1557" t="n">
         <v>13522016</v>
@@ -45609,7 +45609,7 @@
         <v>1.57449996471405</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.22324085235596</v>
+        <v>1.22324073314667</v>
       </c>
       <c r="H1560" t="n">
         <v>7141583</v>
@@ -45638,7 +45638,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.2181910276413</v>
+        <v>1.21819090843201</v>
       </c>
       <c r="H1561" t="n">
         <v>7261987</v>
@@ -45667,7 +45667,7 @@
         <v>1.54050004482269</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.19682610034943</v>
+        <v>1.19682598114014</v>
       </c>
       <c r="H1562" t="n">
         <v>9367065</v>
@@ -45812,7 +45812,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.24072122573853</v>
+        <v>1.24072134494781</v>
       </c>
       <c r="H1567" t="n">
         <v>10187114</v>
@@ -45870,7 +45870,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.17235338687897</v>
+        <v>1.17235350608826</v>
       </c>
       <c r="H1569" t="n">
         <v>22144390</v>
@@ -46015,7 +46015,7 @@
         <v>1.54299998283386</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.19876825809479</v>
+        <v>1.19876837730408</v>
       </c>
       <c r="H1574" t="n">
         <v>12998999</v>
@@ -46102,7 +46102,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.17468416690826</v>
+        <v>1.17468404769897</v>
       </c>
       <c r="H1577" t="n">
         <v>7850490</v>
@@ -46160,7 +46160,7 @@
         <v>1.5</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.16536128520966</v>
+        <v>1.16536140441895</v>
       </c>
       <c r="H1579" t="n">
         <v>11634126</v>
@@ -46334,7 +46334,7 @@
         <v>1.50849997997284</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.17196500301361</v>
+        <v>1.17196488380432</v>
       </c>
       <c r="H1585" t="n">
         <v>7212191</v>
@@ -46421,7 +46421,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.216637134552</v>
+        <v>1.21663725376129</v>
       </c>
       <c r="H1588" t="n">
         <v>9449143</v>
@@ -46508,7 +46508,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.20187604427338</v>
+        <v>1.20187592506409</v>
       </c>
       <c r="H1591" t="n">
         <v>6526192</v>
@@ -46566,7 +46566,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.23839068412781</v>
+        <v>1.23839056491852</v>
       </c>
       <c r="H1593" t="n">
         <v>10352421</v>
@@ -46653,7 +46653,7 @@
         <v>1.69249999523163</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.31491589546204</v>
+        <v>1.31491601467133</v>
       </c>
       <c r="H1596" t="n">
         <v>15239132</v>
@@ -46740,7 +46740,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.29510509967804</v>
+        <v>1.29510498046875</v>
       </c>
       <c r="H1599" t="n">
         <v>4479022</v>
@@ -46769,7 +46769,7 @@
         <v>1.65649998188019</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.28694725036621</v>
+        <v>1.28694713115692</v>
       </c>
       <c r="H1600" t="n">
         <v>6524688</v>
@@ -46827,7 +46827,7 @@
         <v>1.6764999628067</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.30248546600342</v>
+        <v>1.30248534679413</v>
       </c>
       <c r="H1602" t="n">
         <v>6427462</v>
@@ -46856,7 +46856,7 @@
         <v>1.64549994468689</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.27840137481689</v>
+        <v>1.2784012556076</v>
       </c>
       <c r="H1603" t="n">
         <v>8047828</v>
@@ -46885,7 +46885,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.26092088222504</v>
+        <v>1.26092100143433</v>
       </c>
       <c r="H1604" t="n">
         <v>4698684</v>
@@ -47204,7 +47204,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.26635921001434</v>
+        <v>1.26635932922363</v>
       </c>
       <c r="H1615" t="n">
         <v>6580026</v>
@@ -47233,7 +47233,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.28189754486084</v>
+        <v>1.28189742565155</v>
       </c>
       <c r="H1616" t="n">
         <v>5026658</v>
@@ -47291,7 +47291,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.27179753780365</v>
+        <v>1.27179765701294</v>
       </c>
       <c r="H1618" t="n">
         <v>9340094</v>
@@ -47494,7 +47494,7 @@
         <v>1.62950003147125</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.33862912654877</v>
+        <v>1.33862900733948</v>
       </c>
       <c r="H1625" t="n">
         <v>11168418</v>
@@ -47552,7 +47552,7 @@
         <v>1.60150003433228</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.3156270980835</v>
+        <v>1.31562697887421</v>
       </c>
       <c r="H1627" t="n">
         <v>9309782</v>
@@ -47581,7 +47581,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.32178819179535</v>
+        <v>1.32178831100464</v>
       </c>
       <c r="H1628" t="n">
         <v>4633675</v>
@@ -47639,7 +47639,7 @@
         <v>1.57749998569489</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.29591119289398</v>
+        <v>1.29591107368469</v>
       </c>
       <c r="H1630" t="n">
         <v>7298771</v>
@@ -47726,7 +47726,7 @@
         <v>1.52849996089935</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.25565779209137</v>
+        <v>1.25565767288208</v>
       </c>
       <c r="H1633" t="n">
         <v>4319048</v>
@@ -47900,7 +47900,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.13284397125244</v>
+        <v>1.13284385204315</v>
       </c>
       <c r="H1639" t="n">
         <v>26511105</v>
@@ -48161,7 +48161,7 @@
         <v>1.22650003433228</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.00756585597992</v>
+        <v>1.00756573677063</v>
       </c>
       <c r="H1648" t="n">
         <v>19311358</v>
@@ -48364,7 +48364,7 @@
         <v>1.23849999904633</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.01742362976074</v>
+        <v>1.01742374897003</v>
       </c>
       <c r="H1655" t="n">
         <v>5231585</v>
@@ -48393,7 +48393,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.998939990997314</v>
+        <v>0.998940110206604</v>
       </c>
       <c r="H1656" t="n">
         <v>9488753</v>
@@ -48451,7 +48451,7 @@
         <v>1.244500041008</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.0223525762558</v>
+        <v>1.02235269546509</v>
       </c>
       <c r="H1658" t="n">
         <v>6668573</v>
@@ -49176,7 +49176,7 @@
         <v>1.25849997997284</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.03385365009308</v>
+        <v>1.03385376930237</v>
       </c>
       <c r="H1683" t="n">
         <v>3733073</v>
@@ -49292,7 +49292,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.0523374080658</v>
+        <v>1.05233752727509</v>
       </c>
       <c r="H1687" t="n">
         <v>5388768</v>
@@ -49379,7 +49379,7 @@
         <v>1.244500041008</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.0223525762558</v>
+        <v>1.02235269546509</v>
       </c>
       <c r="H1690" t="n">
         <v>2988164</v>
@@ -49408,7 +49408,7 @@
         <v>1.23549997806549</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.01495921611786</v>
+        <v>1.01495909690857</v>
       </c>
       <c r="H1691" t="n">
         <v>2941520</v>
@@ -49437,7 +49437,7 @@
         <v>1.22950005531311</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.01003038883209</v>
+        <v>1.0100302696228</v>
       </c>
       <c r="H1692" t="n">
         <v>4936716</v>
@@ -49495,7 +49495,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.951293230056763</v>
+        <v>0.951293289661407</v>
       </c>
       <c r="H1694" t="n">
         <v>10324335</v>
@@ -49582,7 +49582,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.903646469116211</v>
+        <v>0.903646528720856</v>
       </c>
       <c r="H1697" t="n">
         <v>7913348</v>
@@ -49611,7 +49611,7 @@
         <v>1.125</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.924183785915375</v>
+        <v>0.92418384552002</v>
       </c>
       <c r="H1698" t="n">
         <v>6517138</v>
@@ -50075,7 +50075,7 @@
         <v>1.03250002861023</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.848195493221283</v>
+        <v>0.848195433616638</v>
       </c>
       <c r="H1714" t="n">
         <v>5817973</v>
@@ -50162,7 +50162,7 @@
         <v>0.991800010204315</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.814760446548462</v>
+        <v>0.814760506153107</v>
       </c>
       <c r="H1717" t="n">
         <v>8288204</v>
@@ -50220,7 +50220,7 @@
         <v>1.02149999141693</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.839158952236176</v>
+        <v>0.839158892631531</v>
       </c>
       <c r="H1719" t="n">
         <v>5609741</v>
@@ -50307,7 +50307,7 @@
         <v>0.991199970245361</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.814267516136169</v>
+        <v>0.814267575740814</v>
       </c>
       <c r="H1722" t="n">
         <v>9404538</v>
@@ -50365,7 +50365,7 @@
         <v>0.983399987220764</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.807859897613525</v>
+        <v>0.807859838008881</v>
       </c>
       <c r="H1724" t="n">
         <v>5587654</v>
@@ -50510,7 +50510,7 @@
         <v>1.02149999141693</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.839158952236176</v>
+        <v>0.839158892631531</v>
       </c>
       <c r="H1729" t="n">
         <v>7204572</v>
@@ -50539,7 +50539,7 @@
         <v>1.02649998664856</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.843266487121582</v>
+        <v>0.843266427516937</v>
       </c>
       <c r="H1730" t="n">
         <v>5883271</v>
@@ -50568,7 +50568,7 @@
         <v>1.02649998664856</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.843266487121582</v>
+        <v>0.843266427516937</v>
       </c>
       <c r="H1731" t="n">
         <v>7494448</v>
@@ -50626,7 +50626,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.831354677677155</v>
+        <v>0.831354737281799</v>
       </c>
       <c r="H1733" t="n">
         <v>4302329</v>
@@ -50713,7 +50713,7 @@
         <v>1.10150003433228</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.904878735542297</v>
+        <v>0.904878675937653</v>
       </c>
       <c r="H1736" t="n">
         <v>11761738</v>
@@ -50742,7 +50742,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.937327742576599</v>
+        <v>0.937327802181244</v>
       </c>
       <c r="H1737" t="n">
         <v>15744992</v>
@@ -50771,7 +50771,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.926648259162903</v>
+        <v>0.926648318767548</v>
       </c>
       <c r="H1738" t="n">
         <v>7912040</v>
@@ -50800,7 +50800,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.921719312667847</v>
+        <v>0.921719253063202</v>
       </c>
       <c r="H1739" t="n">
         <v>7364006</v>
@@ -50829,7 +50829,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.922540962696075</v>
+        <v>0.922540903091431</v>
       </c>
       <c r="H1740" t="n">
         <v>7150382</v>
@@ -50858,7 +50858,7 @@
         <v>1.12249994277954</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.922129929065704</v>
+        <v>0.922130048274994</v>
       </c>
       <c r="H1741" t="n">
         <v>4587256</v>
@@ -50916,7 +50916,7 @@
         <v>1.12950003147125</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.927880585193634</v>
+        <v>0.927880525588989</v>
       </c>
       <c r="H1743" t="n">
         <v>10660608</v>
@@ -50945,7 +50945,7 @@
         <v>1.15450000762939</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.948417961597443</v>
+        <v>0.948417901992798</v>
       </c>
       <c r="H1744" t="n">
         <v>9234285</v>
@@ -51032,7 +51032,7 @@
         <v>1.22950005531311</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.01003038883209</v>
+        <v>1.0100302696228</v>
       </c>
       <c r="H1747" t="n">
         <v>10353857</v>
@@ -51235,7 +51235,7 @@
         <v>1.30350005626678</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.07082104682922</v>
+        <v>1.07082092761993</v>
       </c>
       <c r="H1754" t="n">
         <v>9230551</v>
@@ -51264,7 +51264,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.06712424755096</v>
+        <v>1.06712436676025</v>
       </c>
       <c r="H1755" t="n">
         <v>6298663</v>
@@ -51409,7 +51409,7 @@
         <v>1.29949998855591</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.06753504276276</v>
+        <v>1.06753492355347</v>
       </c>
       <c r="H1760" t="n">
         <v>7113639</v>
@@ -51438,7 +51438,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.04905128479004</v>
+        <v>1.04905140399933</v>
       </c>
       <c r="H1761" t="n">
         <v>11193207</v>
@@ -51467,7 +51467,7 @@
         <v>1.29050004482269</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.06014168262482</v>
+        <v>1.06014156341553</v>
       </c>
       <c r="H1762" t="n">
         <v>10039601</v>
@@ -51496,7 +51496,7 @@
         <v>1.31149995326996</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.07739293575287</v>
+        <v>1.07739305496216</v>
       </c>
       <c r="H1763" t="n">
         <v>10046442</v>
@@ -51525,7 +51525,7 @@
         <v>1.31949996948242</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.08396482467651</v>
+        <v>1.0839649438858</v>
       </c>
       <c r="H1764" t="n">
         <v>9235825</v>
@@ -51612,7 +51612,7 @@
         <v>1.30550003051758</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.07246387004852</v>
+        <v>1.07246398925781</v>
       </c>
       <c r="H1767" t="n">
         <v>4587307</v>
@@ -51757,7 +51757,7 @@
         <v>1.29750001430511</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.06589210033417</v>
+        <v>1.06589198112488</v>
       </c>
       <c r="H1772" t="n">
         <v>10479548</v>
@@ -51786,7 +51786,7 @@
         <v>1.26950001716614</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.04289031028748</v>
+        <v>1.04289019107819</v>
       </c>
       <c r="H1773" t="n">
         <v>13966254</v>
@@ -52047,7 +52047,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.02276349067688</v>
+        <v>1.02276337146759</v>
       </c>
       <c r="H1782" t="n">
         <v>5079187</v>
@@ -52366,7 +52366,7 @@
         <v>1.39450001716614</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.14557719230652</v>
+        <v>1.14557731151581</v>
       </c>
       <c r="H1793" t="n">
         <v>6515230</v>
@@ -52453,7 +52453,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.11887848377228</v>
+        <v>1.11887860298157</v>
       </c>
       <c r="H1796" t="n">
         <v>13930154</v>
@@ -52511,7 +52511,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.12791514396667</v>
+        <v>1.12791502475739</v>
       </c>
       <c r="H1798" t="n">
         <v>8427374</v>
@@ -52685,7 +52685,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.13284397125244</v>
+        <v>1.13284385204315</v>
       </c>
       <c r="H1804" t="n">
         <v>27064479</v>
@@ -52888,7 +52888,7 @@
         <v>1.40450000762939</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.15379226207733</v>
+        <v>1.15379238128662</v>
       </c>
       <c r="H1811" t="n">
         <v>8486975</v>
@@ -53120,7 +53120,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.13777303695679</v>
+        <v>1.1377729177475</v>
       </c>
       <c r="H1819" t="n">
         <v>11303255</v>
@@ -53149,7 +53149,7 @@
         <v>1.37049996852875</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.125861287117</v>
+        <v>1.12586116790771</v>
       </c>
       <c r="H1820" t="n">
         <v>9623962</v>
@@ -53294,7 +53294,7 @@
         <v>1.3585000038147</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.11600339412689</v>
+        <v>1.1160032749176</v>
       </c>
       <c r="H1825" t="n">
         <v>20210477</v>
@@ -53352,7 +53352,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.13284397125244</v>
+        <v>1.13284385204315</v>
       </c>
       <c r="H1827" t="n">
         <v>6554286</v>
@@ -53381,7 +53381,7 @@
         <v>1.3914999961853</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.14311277866364</v>
+        <v>1.14311265945435</v>
       </c>
       <c r="H1828" t="n">
         <v>16730300</v>
@@ -53439,7 +53439,7 @@
         <v>1.37650001049042</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.13079023361206</v>
+        <v>1.13079011440277</v>
       </c>
       <c r="H1830" t="n">
         <v>6523463</v>
@@ -53497,7 +53497,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.11477100849152</v>
+        <v>1.11477112770081</v>
       </c>
       <c r="H1832" t="n">
         <v>9082610</v>
@@ -53555,7 +53555,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.13777303695679</v>
+        <v>1.1377729177475</v>
       </c>
       <c r="H1834" t="n">
         <v>9509963</v>
@@ -53758,7 +53758,7 @@
         <v>1.45550000667572</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.19568860530853</v>
+        <v>1.19568848609924</v>
       </c>
       <c r="H1841" t="n">
         <v>7124666</v>
@@ -53874,7 +53874,7 @@
         <v>1.42299997806549</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.168989777565</v>
+        <v>1.16898989677429</v>
       </c>
       <c r="H1845" t="n">
         <v>13947761</v>
@@ -53932,7 +53932,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.20760011672974</v>
+        <v>1.20760023593903</v>
       </c>
       <c r="H1847" t="n">
         <v>14809112</v>
@@ -53961,7 +53961,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1848" t="n">
-        <v>1.20102822780609</v>
+        <v>1.2010281085968</v>
       </c>
       <c r="H1848" t="n">
         <v>7750459</v>
@@ -54019,7 +54019,7 @@
         <v>1.50349998474121</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.23512029647827</v>
+        <v>1.23512041568756</v>
       </c>
       <c r="H1850" t="n">
         <v>17142495</v>
@@ -54048,7 +54048,7 @@
         <v>1.52849996089935</v>
       </c>
       <c r="G1851" t="n">
-        <v>1.25565779209137</v>
+        <v>1.25565767288208</v>
       </c>
       <c r="H1851" t="n">
         <v>9969681</v>
@@ -54106,7 +54106,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1853" t="n">
-        <v>1.27167701721191</v>
+        <v>1.2716771364212</v>
       </c>
       <c r="H1853" t="n">
         <v>11550973</v>
@@ -54193,7 +54193,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.26099753379822</v>
+        <v>1.26099741458893</v>
       </c>
       <c r="H1856" t="n">
         <v>8214970</v>
@@ -54222,7 +54222,7 @@
         <v>1.53250002861023</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.25894379615784</v>
+        <v>1.25894367694855</v>
       </c>
       <c r="H1857" t="n">
         <v>7912409</v>
@@ -54541,7 +54541,7 @@
         <v>1.58949995040894</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.30576908588409</v>
+        <v>1.3057689666748</v>
       </c>
       <c r="H1868" t="n">
         <v>6588494</v>
@@ -54657,7 +54657,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.34807634353638</v>
+        <v>1.34807622432709</v>
       </c>
       <c r="H1872" t="n">
         <v>10285727</v>
@@ -54686,7 +54686,7 @@
         <v>1.66250002384186</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.36573839187622</v>
+        <v>1.36573827266693</v>
       </c>
       <c r="H1873" t="n">
         <v>16983654</v>
@@ -54715,7 +54715,7 @@
         <v>1.69149994850159</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.38956165313721</v>
+        <v>1.3895617723465</v>
       </c>
       <c r="H1874" t="n">
         <v>17208967</v>
@@ -54744,7 +54744,7 @@
         <v>1.70449995994568</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.4002411365509</v>
+        <v>1.40024125576019</v>
       </c>
       <c r="H1875" t="n">
         <v>14267156</v>
@@ -54802,7 +54802,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.37189948558807</v>
+        <v>1.37189960479736</v>
       </c>
       <c r="H1877" t="n">
         <v>11915282</v>
@@ -54860,7 +54860,7 @@
         <v>1.63849997520447</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.34602248668671</v>
+        <v>1.34602236747742</v>
       </c>
       <c r="H1879" t="n">
         <v>18603093</v>
@@ -80064,9 +80064,38 @@
         <v>2.40499997138977</v>
       </c>
       <c r="H2748" t="n">
-        <v>4155760</v>
+        <v>4175282</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>2.43600010871887</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>2.38599991798401</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>2.43600010871887</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>2.43600010871887</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>8904150</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
